--- a/testrail-import/global-search-v2-testrail-import.xlsx
+++ b/testrail-import/global-search-v2-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -439,9 +439,8 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,21 +484,8 @@
           <t>References</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Internal ID</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TestRail Case ID</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>TestRail Link</t>
-        </is>
-      </c>
+      <c r="I1" s="1" t="inlineStr"/>
+      <c r="J1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -549,17 +535,8 @@
           <t>requirements.md 5.1 Trigger and Surface; 8 Functional Requirements</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-01</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -607,17 +584,8 @@
           <t>requirements.md 5.1 Trigger and Surface</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-02</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -663,17 +631,8 @@
           <t>requirements.md 5.1; 5.5 Keyboard Navigation</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-03</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -718,17 +677,8 @@
           <t>requirements.md 5.1 (Esc, clicking underlay, or Cmd+K again closes it)</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-04</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -774,17 +724,8 @@
           <t>requirements.md 5.1 (clicking the page underlay closes it)</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-05</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -833,17 +774,8 @@
           <t>requirements.md 5.5 (Up/Down moves focus through visible rows, skipping group headers)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-06</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -889,17 +821,8 @@
           <t>requirements.md 5.5 (Enter opens the focused row in the same tab)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-07</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -945,17 +868,8 @@
           <t>requirements.md 5.5 (Cmd+Enter or Ctrl+Enter opens in a new browser tab)</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-08</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1005,17 +919,8 @@
           <t>requirements.md 5.5 (Tab moves focus to the scope tab strip; Left/Right cycles tabs when focus is on the tab strip)</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-09</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1061,17 +966,8 @@
           <t>requirements.md 5.1 (footer always shows the keyboard legend)</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>GS-KEY-10</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1115,17 +1011,8 @@
           <t>requirements.md 5.2 State 3 (tab strip); design-notes cross-reference</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>GS-TAB-01</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1172,17 +1059,8 @@
           <t>requirements.md 5.2 State 3; 6.2 group order</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>GS-TAB-02</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1227,17 +1105,8 @@
           <t>requirements.md 5.2 State 3 (selecting a tab scopes the query to that entity type)</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>GS-TAB-03</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1282,17 +1151,8 @@
           <t>requirements.md 5.2 State 3</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>GS-TAB-04</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1337,17 +1197,8 @@
           <t>requirements.md 5.2 State 3</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>GS-TAB-05</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1392,17 +1243,8 @@
           <t>requirements.md 5.2 State 3</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>GS-TAB-06</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1447,17 +1289,8 @@
           <t>requirements.md 5.2 State 3</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>GS-TAB-07</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1503,17 +1336,8 @@
           <t>requirements.md 4 (Part Sales is a NEW searchable entity); 5.2 State 3</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>GS-TAB-08</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1559,17 +1383,8 @@
           <t>requirements.md 5.2 State 3 (results grouped by entity type with a count)</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>GS-GRP-01</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1615,17 +1430,8 @@
           <t>requirements.md 1 (old = 3 per category); 5.2 State 3 (up to 5 results)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>GS-GRP-02</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1671,17 +1477,8 @@
           <t>requirements.md 5.2 State 3 ('Show all N work orders' link)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>GS-GRP-03</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1727,17 +1524,8 @@
           <t>requirements.md 5.2 (Show all switches to the scope tab - recommended); Open Question OQ-SPEC-1</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>GS-GRP-04</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1783,17 +1571,8 @@
           <t>requirements.md 6.2 (group display order in 'All')</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>GS-GRP-05</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1839,17 +1618,8 @@
           <t>requirements.md 5.3 (matched substring highlighted)</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>GS-GRP-06</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1895,17 +1665,8 @@
           <t>requirements.md 9 Non-Functional (screen-reader announcements when results count changes; focus rings)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>GS-GRP-07</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1954,17 +1715,8 @@
           <t>requirements.md 4 Work Orders (Displayed: WO number + customer, status badge, lead technician, asset/unit, date)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>GS-ENT-01</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2012,17 +1764,8 @@
           <t>requirements.md 4 Customers (Displayed: name, address line, open WO count badge, telephone on hover)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>GS-ENT-02</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2069,17 +1812,8 @@
           <t>requirements.md 4 Assets (Displayed: year + make + model primary, customer name secondary)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>GS-ENT-03</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2128,17 +1862,8 @@
           <t>requirements.md 4 Parts (Displayed: description, part number, total quantity with stock-status color)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>GS-ENT-04</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2185,17 +1910,8 @@
           <t>requirements.md 4 Vendors (Displayed: vendor name primary, address line secondary)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>GS-ENT-05</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2243,17 +1959,8 @@
           <t>requirements.md 4 Part Sales (Displayed: P-number + customer primary, status badge, total price + created date)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>GS-ENT-06</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2299,17 +2006,8 @@
           <t>requirements.md 4 (secondary line shows 'Contact/info match')</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>GS-ENT-07</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2355,17 +2053,8 @@
           <t>requirements.md 5.3 (status badge colors, same tokens as the WO list)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>GS-ENT-08</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2411,17 +2100,8 @@
           <t>requirements.md 7 (token n-gram / trigram matching catches Petersn -&gt; Peterson)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-01</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2466,17 +2146,8 @@
           <t>requirements.md 1 + 10 Phase 5 (fuzzy query 'Abrige')</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-02</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2521,17 +2192,8 @@
           <t>requirements.md 7 (Damerau-Levenshtein; freihgtliner -&gt; freightliner)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-03</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2576,17 +2238,8 @@
           <t>requirements.md 7 (phonetic fallback catches Filbridge -&gt; Fibridge)</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-04</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2634,17 +2287,8 @@
           <t>requirements.md 7 (S2-15276 = s215276); identifier fields are exact-only</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-05</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2690,17 +2334,8 @@
           <t>requirements.md 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-06</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2747,17 +2382,8 @@
           <t>requirements.md 7 (phone normalization); 4 (Contact/info match affordance)</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-07</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2803,17 +2429,8 @@
           <t>requirements.md 7 (What is NOT fuzzy: part number)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-08</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2859,17 +2476,8 @@
           <t>requirements.md 7 (exact identifier fields bypass fuzzy logic)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-09</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2915,17 +2523,8 @@
           <t>requirements.md 7 (fuzzy soft-match highlight treatment - design polish, confirm with design)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-10</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2971,17 +2570,8 @@
           <t>requirements.md 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>GS-FUZ-11</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3027,17 +2617,8 @@
           <t>requirements.md 6.2 (ID match &gt; 0.95 pinned at top)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>GS-RANK-01</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3083,17 +2664,8 @@
           <t>requirements.md 6.1 Work Orders signals (open status +0.30, recency, assigned/viewed, old-closed demoted)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>GS-RANK-02</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3139,17 +2711,8 @@
           <t>requirements.md 6.1 Parts signals</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>GS-RANK-03</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3195,17 +2758,8 @@
           <t>requirements.md 6.3 Contextual bias</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>GS-RANK-04</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3251,17 +2805,8 @@
           <t>requirements.md 6.3 Contextual bias</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>GS-RANK-05</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3309,17 +2854,8 @@
           <t>requirements.md 5.2 State 1 (First-time search)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>GS-EMPTY-01</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3367,17 +2903,8 @@
           <t>requirements.md 5.2 State 1 (quick-create chips)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>GS-EMPTY-02</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3424,17 +2951,8 @@
           <t>requirements.md 5.2 State 2 (Recent searches grouped by interval); 8 (persist recent-entity-views 30 days)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>GS-REC-01</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3481,17 +2999,8 @@
           <t>requirements.md 5.2 State 2 (same row template as a result row)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>GS-REC-02</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3536,17 +3045,8 @@
           <t>requirements.md 10 Phase 4 (records a touch on every result click / entity-page visit)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>GS-REC-03</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3593,17 +3093,8 @@
           <t>requirements.md 5.2 State 5 (Persisting search); 8 (persist last query, rehydrate on reopen)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>GS-PERS-01</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3650,17 +3141,8 @@
           <t>requirements.md 5.2 State 5 (Reopening restores the query, the scope tab, and the result list)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>GS-PERS-02</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3706,17 +3188,8 @@
           <t>requirements.md 5.2 State 5; design-notes screenshot 9 (clearable via the x button)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>GS-PERS-03</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3763,17 +3236,8 @@
           <t>requirements.md 5.2 State 4 (No results for &lt;query&gt; + quick-create chips)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>GS-NORES-01</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3818,17 +3282,8 @@
           <t>requirements.md 5.2 State 4</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>GS-NORES-02</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3874,17 +3329,8 @@
           <t>requirements.md 5.4 (Work Order -&gt; 'Add new line', only when currently editing a WO elsewhere)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>GS-HOVER-01</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3931,17 +3377,8 @@
           <t>requirements.md 5.4 (Asset -&gt; 'New work order' + clock (history) and Invoice icons)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>GS-HOVER-02</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3988,17 +3425,8 @@
           <t>requirements.md 5.4 (Customer -&gt; 'New work order', 'New contact')</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>GS-HOVER-03</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4045,17 +3473,8 @@
           <t>requirements.md 5.4 (Part -&gt; 'Add part' when not currently editing a WO)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>GS-HOVER-04</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4101,17 +3520,8 @@
           <t>requirements.md 5.4 (Vendor -&gt; 'Add contact')</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>GS-HOVER-05</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4158,17 +3568,8 @@
           <t>requirements.md 5.4 (Part -&gt; 'Add to work order' only when currently editing a WO)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>GS-HOVER-06</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4213,17 +3614,8 @@
           <t>requirements.md 5.4 (Quick actions never trigger destructive operations; hover state non-essential)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>GS-HOVER-07</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4271,17 +3663,8 @@
           <t>design-notes screenshot 1 (in-page Work Orders list search banner)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>GS-LIST-01</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4326,17 +3709,8 @@
           <t>design-notes screenshot 1</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>GS-LIST-02</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4384,17 +3758,8 @@
           <t>requirements.md 8 (tolerate offline/network failures with an inline 'Search unavailable, retry' banner)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>GS-ERR-01</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4440,17 +3805,8 @@
           <t>requirements.md 9 (all result fields respect role-based-access checks)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>GS-PERM-01</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4497,17 +3853,8 @@
           <t>requirements.md 9 (a technician without Parts access does not see Parts results)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>GS-PERM-02</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4553,17 +3900,8 @@
           <t>requirements.md 9 (all result fields respect role-based-access checks)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>GS-PERM-03</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4609,17 +3947,8 @@
           <t>requirements.md 9 (all result fields respect existing tenant-isolation checks)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>GS-PERM-04</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4667,17 +3996,8 @@
           <t>requirements.md 9 (must work for a single-tenant dataset where any entity type is empty, e.g. no part sales yet)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>GS-PERM-05</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4724,17 +4044,8 @@
           <t>requirements.md 10 Phase 1 (GET /api/search; scope=all)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-01</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4782,17 +4093,8 @@
           <t>requirements.md 10 Phase 1 (scope parameter)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-02</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4840,17 +4142,8 @@
           <t>requirements.md 10 Phase 1 (limit default 5; response includes per-group totals)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-03</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4899,17 +4192,8 @@
           <t>requirements.md 7 (identifier normalization); 6.2 (ID match pinned)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-04</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4955,17 +4239,8 @@
           <t>requirements.md 7 (What is NOT fuzzy)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-05</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5013,17 +4288,8 @@
           <t>requirements.md 9 (results respect role-based-access checks - enforced server-side)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-06</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5071,17 +4337,8 @@
           <t>requirements.md 8 (offline/network failure handling)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-07</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5128,17 +4385,8 @@
           <t>requirements.md 6.2 (group order); 10 Phase 1 (per-item metadata)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-08</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5186,17 +4434,8 @@
           <t>requirements.md 10 Phase 1 (cursor parameter)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-09</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5243,17 +4482,8 @@
           <t>requirements.md 6.3 (contextual bias); 10 Phase 1 (context parameter)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-10</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5300,17 +4530,8 @@
           <t>requirements.md 8 (persist recent-entity-views 30 days); 10 Phase 4</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-11</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5357,17 +4578,8 @@
           <t>requirements.md 8 (debounce input at 150ms; render within 200ms p95)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>GS-API-12</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>pending push</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/global-search-v2-testrail-import.xlsx
+++ b/testrail-import/global-search-v2-testrail-import.xlsx
@@ -676,15 +676,33 @@
 a
 d
 s
+a
+p
+l
+a
+i
+n
+s
+e
+a
+r
+c
+h
+p
+l
+a
+c
+e
+h
+o
+l
+d
+e
+r
+(
+n
+o
 '
-S
-e
-a
-r
-c
-h
-o
-r
 a
 s
 k
@@ -698,6 +716,45 @@
 o
 n
 '
+/
+A
+I
+w
+o
+r
+d
+i
+n
+g
+i
+n
+v
+1
+-
+e
+x
+a
+c
+t
+c
+o
+p
+y
+p
+e
+r
+t
+h
+e
+v
+2
+d
+e
+s
+i
+g
+n
+)
 .
 5
 .
@@ -1228,15 +1285,33 @@
 d
 e
 r
+a
+p
+l
+a
+i
+n
+s
+e
+a
+r
+c
+h
+p
+l
+a
+c
+e
+h
+o
+l
+d
+e
+r
+(
+n
+o
 '
-S
-e
-a
-r
-c
-h
-o
-r
 a
 s
 k
@@ -1250,6 +1325,45 @@
 o
 n
 '
+/
+A
+I
+w
+o
+r
+d
+i
+n
+g
+i
+n
+v
+1
+-
+e
+x
+a
+c
+t
+c
+o
+p
+y
+p
+e
+r
+t
+h
+e
+v
+2
+d
+e
+s
+i
+g
+n
+)
 .
 4
 .
@@ -5199,6 +5313,15 @@
 r
 s
 ,
+C
+o
+n
+t
+a
+c
+t
+s
+,
 A
 s
 s
@@ -5229,6 +5352,56 @@
 l
 e
 s
+,
+P
+u
+r
+c
+h
+a
+s
+e
+O
+r
+d
+e
+r
+s
+,
+V
+e
+n
+d
+o
+r
+I
+n
+v
+o
+i
+c
+e
+s
+(
+v
+2
+n
+i
+n
+e
+e
+n
+t
+i
+t
+i
+e
+s
+,
+D
+1
+6
+)
 .
 2
 .
@@ -5262,6 +5435,83 @@
 u
 l
 t
+.
+3
+.
+A
+t
+a
+b
+i
+s
+s
+h
+o
+w
+n
+o
+n
+l
+y
+f
+o
+r
+a
+n
+e
+n
+t
+i
+t
+y
+t
+y
+p
+e
+t
+h
+e
+u
+s
+e
+r
+h
+a
+s
+p
+e
+r
+m
+i
+s
+s
+i
+o
+n
+t
+o
+s
+e
+e
+(
+p
+e
+r
+m
+i
+s
+s
+i
+o
+n
+-
+s
+c
+o
+p
+e
+d
+)
 .
 -
 -
@@ -5629,6 +5879,10 @@
 t
 h
 a
+t
+r
+u
+e
 c
 o
 u
@@ -5650,7 +5904,7 @@
 o
 r
 k
-o
+O
 r
 d
 e
@@ -5697,11 +5951,25 @@
 t
 h
 e
-o
-r
-d
-e
-r
+v
+2
+n
+i
+n
+e
+-
+e
+n
+t
+i
+t
+y
+o
+r
+d
+e
+r
+:
 W
 o
 r
@@ -5723,6 +5991,15 @@
 r
 s
 ,
+C
+o
+n
+t
+a
+c
+t
+s
+,
 A
 s
 s
@@ -5753,6 +6030,41 @@
 l
 e
 s
+,
+P
+u
+r
+c
+h
+a
+s
+e
+O
+r
+d
+e
+r
+s
+,
+V
+e
+n
+d
+o
+r
+I
+n
+v
+o
+i
+c
+e
+s
+(
+D
+1
+6
+)
 .
 -
 -
@@ -10113,50 +10425,15 @@
         <is>
           <t xml:space="preserve">1
 .
-A
-l
-i
-n
-k
-a
-p
-p
-e
-a
-r
-s
-a
-t
-t
-h
-e
-b
-o
-t
-t
-o
-m
-o
-f
-t
-h
-e
-g
-r
-o
-u
-p
-,
-w
-o
-r
-d
-e
-d
-l
-i
-k
-e
+T
+h
+e
+r
+e
+i
+s
+N
+O
 '
 S
 h
@@ -10165,102 +10442,200 @@
 a
 l
 l
+N
+'
+l
+i
+n
+k
+i
+n
+v
+2
+(
+d
+r
+o
+p
+p
+e
+d
+b
+y
+D
+1
+5
+/
+F
+R
+-
+0
+1
+3
+)
+.
+2
+.
+I
+n
+t
+h
+e
+A
+l
+l
+v
+i
+e
 w
+a
+g
+r
+o
+u
+p
+s
+h
+o
+w
+s
+u
+p
+t
+o
+5
+r
+o
+w
+s
+w
+i
+t
+h
+i
+t
+s
+t
+r
+u
+e
+t
+o
+t
+a
+l
+i
+n
+t
+h
+e
+h
+e
+a
+d
+i
+n
+g
+(
+f
+o
+r
+e
+x
+a
+m
+p
+l
+e
+'
+W
 o
 r
 k
-o
-r
-d
-e
-r
-s
-'
+O
+r
+d
+e
+r
+s
 (
-o
-r
-'
-S
-h
-o
-w
-a
-l
-l
-1
-2
-w
-o
-r
-k
-o
-r
-d
-e
-r
-s
+1
+2
+)
 '
 )
 .
-2
+3
 .
 T
-h
-e
-l
-i
-n
-k
-o
-n
-l
+o
+s
+e
+e
+m
+o
+r
+e
+t
+h
+a
+n
+5
+,
+t
+h
+e
+u
+s
+e
+r
+o
+p
+e
+n
+s
+t
+h
+a
+t
+e
+n
+t
+i
+t
 y
-a
-p
-p
-e
-a
-r
-s
-w
-h
-e
-n
-t
-h
-e
-r
-e
-a
-r
-e
-m
-o
-r
-e
-m
-a
-t
-c
-h
-e
-s
-t
-h
-a
-n
-t
-h
-e
-r
-o
-w
-s
-s
-h
-o
-w
-n
+'
+s
+s
+c
+o
+p
+e
+t
+a
+b
+(
+s
+e
+e
+t
+h
+e
+S
+c
+o
+p
+e
+T
+a
+b
+s
+c
+a
+s
+e
+s
+)
 .
 -
 -
@@ -10541,239 +10916,240 @@
         <is>
           <t xml:space="preserve">1
 .
+O
+p
+e
+n
+i
+n
+g
+a
+n
+e
+n
+t
+i
+t
+y
+'
+s
+s
+c
+o
+p
+e
+t
+a
+b
+(
+n
+o
+t
+a
+'
+S
+h
+o
+w
+a
+l
+l
+'
+l
+i
+n
+k
+,
+w
+h
+i
+c
+h
+n
+o
+l
+o
+n
+g
+e
+r
+e
+x
+i
+s
+t
+s
+)
+s
+h
+o
+w
+s
+t
+h
+a
+t
+e
+n
+t
+i
+t
+y
+'
+s
+f
+u
+l
+l
+r
+e
+s
+u
+l
+t
+l
+i
+s
+t
+w
+i
+t
+h
+i
+n
+t
+h
+e
+m
+o
+d
+a
+l
+.
+2
+.
 T
 h
 e
-p
-a
-l
-e
-t
-t
-e
-s
-t
+s
+c
+o
+p
+e
+d
+l
+i
+s
+t
+l
+o
+a
+d
+s
+a
+d
+e
+f
+a
+u
+l
+t
+p
+a
+g
+e
+(
+2
+5
+)
+w
+i
+t
+h
+c
+u
+r
+s
+o
+r
+-
+b
+a
+s
+e
+d
+l
+o
+a
+d
+-
+m
+o
+r
+e
+i
+n
+s
+i
+d
+e
+t
+h
+e
+m
+o
+d
+a
+l
+.
+3
+.
+T
+h
+e
+m
+o
+d
+a
+l
+d
+o
+e
+s
+n
+o
+t
+n
+a
+v
+i
+g
+a
+t
+e
+a
+w
 a
 y
-s
-o
-p
-e
-n
-a
-n
-d
-s
-w
-i
-t
-c
-h
-e
-s
-t
-o
-t
-h
-e
-'
-W
-o
-r
-k
-O
-r
-d
-e
-r
-s
-'
-s
-c
-o
-p
-e
-t
-a
-b
-.
-2
-.
-T
-h
+t
+o
+a
+s
+e
+p
+a
+r
+a
+t
 e
 f
 u
 l
 l
-l
-i
-s
-t
-o
-f
-m
-a
-t
-c
-h
-i
-n
-g
-W
-o
-r
-k
-O
-r
-d
-e
-r
-s
-f
-o
-r
-t
-h
-e
-c
-u
-r
-r
-e
-n
-t
-q
-u
-e
-r
-y
-i
-s
-s
-h
-o
-w
-n
-,
-s
-c
-o
-p
-e
-d
-t
-o
-W
-o
-r
-k
-O
-r
-d
-e
-r
-s
-o
-n
-l
-y
-.
-3
-.
-T
-h
-e
-p
-a
-l
-e
-t
-t
-e
-d
-o
-e
-s
-n
-o
-t
-l
-e
-a
-v
-e
-t
-o
-a
-s
-e
-p
-a
-r
-a
-t
-e
-f
-u
-l
-l
-p
-a
-g
-e
-(
-t
-h
-e
-r
-e
-c
-o
-m
-m
-e
-n
-d
-e
-d
-b
-e
-h
-a
-v
-i
-o
-r
-i
-s
-t
-h
-e
-s
-c
-o
-p
-e
-d
-t
-a
-b
-w
-i
-t
-h
-i
-n
-t
-h
-e
-m
-o
-d
-a
-l
-)
+p
+a
+g
+e
 .
 -
 -
@@ -11119,6 +11495,19 @@
 h
 i
 s
+v
+2
+n
+i
+n
+e
+-
+e
+n
+t
+i
+t
+y
 o
 r
 d
@@ -11146,6 +11535,15 @@
 r
 s
 ,
+C
+o
+n
+t
+a
+c
+t
+s
+,
 A
 s
 s
@@ -11176,6 +11574,41 @@
 l
 e
 s
+,
+P
+u
+r
+c
+h
+a
+s
+e
+O
+r
+d
+e
+r
+s
+,
+V
+e
+n
+d
+o
+r
+I
+n
+v
+o
+i
+c
+e
+s
+(
+D
+1
+6
+)
 .
 2
 .
@@ -24695,15 +25128,33 @@
 d
 e
 r
+a
+p
+l
+a
+i
+n
+s
+e
+a
+r
+c
+h
+p
+l
+a
+c
+e
+h
+o
+l
+d
+e
+r
+(
+n
+o
 '
-S
-e
-a
-r
-c
-h
-o
-r
 a
 s
 k
@@ -24717,6 +25168,45 @@
 o
 n
 '
+/
+A
+I
+w
+o
+r
+d
+i
+n
+g
+i
+n
+v
+1
+-
+e
+x
+a
+c
+t
+c
+o
+p
+y
+p
+e
+r
+t
+h
+e
+v
+2
+d
+e
+s
+i
+g
+n
+)
 .
 2
 .
@@ -29366,15 +29856,33 @@
 d
 e
 r
+a
+p
+l
+a
+i
+n
+s
+e
+a
+r
+c
+h
+p
+l
+a
+c
+e
+h
+o
+l
+d
+e
+r
+(
+n
+o
 '
-S
-e
-a
-r
-c
-h
-o
-r
 a
 s
 k
@@ -29388,6 +29896,45 @@
 o
 n
 '
+/
+A
+I
+w
+o
+r
+d
+i
+n
+g
+i
+n
+v
+1
+-
+e
+x
+a
+c
+t
+c
+o
+p
+y
+p
+e
+r
+t
+h
+e
+v
+2
+d
+e
+s
+i
+g
+n
+)
 )
 .
 3
@@ -31825,9 +32372,100 @@
         <is>
           <t xml:space="preserve">1
 .
+O
+n
+h
+o
+v
+e
+r
+a
+P
+a
+r
+t
+q
+u
+i
+c
+k
+a
+c
+t
+i
+o
+n
+a
+p
+p
+e
+a
+r
+s
+:
+"
 A
-n
-'
+d
+d
+t
+o
+w
+o
+r
+k
+o
+r
+d
+e
+r
+"
+w
+h
+e
+n
+y
+o
+u
+a
+r
+e
+c
+u
+r
+r
+e
+n
+t
+l
+y
+e
+d
+i
+t
+i
+n
+g
+a
+w
+o
+r
+k
+o
+r
+d
+e
+r
+,
+o
+t
+h
+e
+r
+w
+i
+s
+e
+"
 A
 d
 d
@@ -31835,29 +32473,59 @@
 a
 r
 t
-'
-b
-u
-t
-t
-o
-n
-a
-p
-p
-e
-a
-r
-s
-o
-n
-h
-o
+"
+.
+2
+.
+T
+h
+e
+P
+a
+r
+t
+r
+o
+w
+n
+a
 v
-e
-r
-.
-2
+i
+g
+a
+t
+e
+s
+t
+o
+I
+N
+V
+E
+N
+T
+O
+R
+Y
+(
+n
+o
+t
+t
+h
+e
+c
+a
+t
+a
+l
+o
+g
+u
+e
+)
+.
+3
 .
 T
 h
@@ -43096,11 +43764,25 @@
 t
 h
 e
-o
-r
-d
-e
-r
+v
+2
+n
+i
+n
+e
+-
+e
+n
+t
+i
+t
+y
+o
+r
+d
+e
+r
+:
 W
 o
 r
@@ -43122,6 +43804,15 @@
 r
 s
 ,
+C
+o
+n
+t
+a
+c
+t
+s
+,
 A
 s
 s
@@ -43152,6 +43843,41 @@
 l
 e
 s
+,
+P
+u
+r
+c
+h
+a
+s
+e
+O
+r
+d
+e
+r
+s
+,
+V
+e
+n
+d
+o
+r
+I
+n
+v
+o
+i
+c
+e
+s
+(
+D
+1
+6
+)
 .
 2
 .
@@ -43202,6 +43928,25 @@
 i
 n
 g
+;
+t
+i
+e
+s
+b
+r
+e
+a
+k
+b
+y
+r
+e
+c
+e
+n
+c
+y
 .
 3
 .
@@ -43287,11 +44032,11 @@
 d
 s
 ,
-s
-t
-a
-t
-u
+b
+a
+d
+g
+e
 s
 /
 q
@@ -43327,6 +44072,29 @@
 c
 h
 e
+s
+,
+a
+n
+d
+t
+r
+u
+e
+p
+e
+r
+-
+g
+r
+o
+u
+p
+t
+o
+t
+a
+l
 s
 .
 -

--- a/testrail-import/global-search-v2-testrail-import.xlsx
+++ b/testrail-import/global-search-v2-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -523,15 +523,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A centered search box (a modal overlay) opens on top of the page.
+          <t>1. A centered search box (a modal overlay) opens on top of the page.
 2. The page behind the box is dimmed.
 3. The search input is focused so you can type right away.
 4. The placeholder reads a plain search placeholder (no 'ask a question' / AI wording in v1 - exact copy per the v2 design).
 5. The footer keyboard legend is visible: 'Navigate' with up/down arrows, 'Select' with the enter symbol, and 'Close esc'.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.1 Trigger and Surface; 8 Functional Requirements, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 Trigger and Surface; 8 Functional Requirements, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -577,14 +576,13 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The centered search box (modal overlay) opens, anchored to the header search field.
+          <t>1. The centered search box (modal overlay) opens, anchored to the header search field.
 2. The page behind is dimmed.
 3. The input is focused and shows the placeholder a plain search placeholder (no 'ask a question' / AI wording in v1 - exact copy per the v2 design).
 4. The footer keyboard legend is visible.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.1 Trigger and Surface, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 Trigger and Surface, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -629,13 +627,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The search box closes.
+          <t>1. The search box closes.
 2. The dimming is removed and you are back on the page you were on.
 3. Keyboard focus returns to the page (or the header search field).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.1; 5.5 Keyboard Navigation, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1; 5.5 Keyboard Navigation, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -680,12 +677,11 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The search box closes.
+          <t>1. The search box closes.
 2. The dimming is removed and you are back on the page.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.1 (Esc, clicking underlay, or Cmd+K again closes it), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 (Esc, clicking underlay, or Cmd+K again closes it), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -731,12 +727,11 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The search box closes.
+          <t>1. The search box closes.
 2. The dimming is removed and you are back on the page.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.1 (clicking the page underlay closes it), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 (clicking the page underlay closes it), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -783,14 +778,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each Down press moves the highlight to the next result row.
+          <t>1. Each Down press moves the highlight to the next result row.
 2. Each Up press moves the highlight to the previous result row.
 3. The highlight moves only across result rows - the group heading lines (for example 'Work orders (12)') are skipped and never get the highlight.
 4. When moving down past the last row of one group, the highlight continues into the first row of the next group.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.5 (Up/Down moves focus through visible rows, skipping group headers), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.5 (Up/Down moves focus through visible rows, skipping group headers), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -836,12 +830,11 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The palette closes and the highlighted record opens in the same browser tab.
+          <t>1. The palette closes and the highlighted record opens in the same browser tab.
 2. You land on that record's page (for example the Work Order detail page).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.5 (Enter opens the focused row in the same tab), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.5 (Enter opens the focused row in the same tab), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -887,12 +880,11 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The highlighted record opens in a NEW browser tab.
+          <t>1. The highlighted record opens in a NEW browser tab.
 2. The page you were on (and, per build behavior, the palette) remains in the original tab.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.5 (Cmd+Enter or Ctrl+Enter opens in a new browser tab), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.5 (Cmd+Enter or Ctrl+Enter opens in a new browser tab), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -940,14 +932,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Pressing Tab moves keyboard focus onto the scope tab strip.
+          <t>1. Pressing Tab moves keyboard focus onto the scope tab strip.
 2. Each Right arrow press moves to the next tab to the right; each Left arrow press moves to the previous tab.
 3. Selecting a tab scopes the results to that entity type.
 4. Focus does not leave the palette (focus stays trapped inside the modal).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.5 (Tab moves focus to the scope tab strip; Left/Right cycles tabs when focus is on the tab strip), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.5 (Tab moves focus to the scope tab strip; Left/Right cycles tabs when focus is on the tab strip), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -993,12 +984,11 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The footer keyboard legend is visible in every state: 'Navigate' with up/down arrows, 'Select' with the enter symbol, and 'Close esc'.
+          <t>1. The footer keyboard legend is visible in every state: 'Navigate' with up/down arrows, 'Select' with the enter symbol, and 'Close esc'.
 2. The legend does not disappear when results are showing or when the input is empty.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.1 (footer always shows the keyboard legend), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 (footer always shows the keyboard legend), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1012,7 +1002,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>The scope tab strip lists All plus the six entity tabs in the exact order</t>
+          <t>The scope tab strip lists All plus all nine entity tabs in the exact order</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1042,18 +1032,19 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The tabs read, in this exact left-to-right order: All, Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (v2 nine entities, D16).
+          <t>1. The tabs read, in this exact left-to-right order: All, Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices.
 2. The 'All' tab is selected by default.
-3. A tab is shown only for an entity type the user has permission to see (permission-scoped).
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3 (tab strip); design-notes cross-reference, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+3. Each tab carries its total result count over the full result set (for example 'All (12)', 'Work Orders (8)').
+4. The strip scrolls horizontally since ten tabs do not fit the 640px modal width.
+5. A tab is shown only for an entity type the user has permission to see.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 (tab strip), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>requirements.md 5.2 State 3 (tab strip); design-notes cross-reference</t>
+          <t>section 5.2 (tab strip)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1095,12 +1086,11 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Results from every matching entity type appear, each under its own group heading with a true count (for example 'Work Orders (12)', 'Customers (2)').
+          <t>1. Results from every matching entity type appear, each under its own group heading with a true count (for example 'Work Orders (12)', 'Customers (2)').
 2. Groups appear in the v2 nine-entity order: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3; 6.2 group order, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3; 6.2 group order, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1145,12 +1135,11 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only Work Order results are shown; other entity groups (Customers, Assets, Parts, Vendors, Part Sales) are hidden.
+          <t>1. Only Work Order results are shown; other entity groups (Customers, Assets, Parts, Vendors, Part Sales) are hidden.
 2. The 'Work Orders' tab appears selected/active.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3 (selecting a tab scopes the query to that entity type), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3 (selecting a tab scopes the query to that entity type), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1195,12 +1184,11 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only Customer results are shown; other entity groups are hidden.
+          <t>1. Only Customer results are shown; other entity groups are hidden.
 2. The 'Customers' tab appears selected/active.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,12 +1233,11 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only Asset results are shown; other entity groups are hidden.
+          <t>1. Only Asset results are shown; other entity groups are hidden.
 2. The 'Assets' tab appears selected/active.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1295,12 +1282,11 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only Part results are shown; other entity groups are hidden.
+          <t>1. Only Part results are shown; other entity groups are hidden.
 2. The 'Parts' tab appears selected/active.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1345,12 +1331,11 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only Vendor results are shown; other entity groups are hidden.
+          <t>1. Only Vendor results are shown; other entity groups are hidden.
 2. The 'Vendors' tab appears selected/active.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1396,12 +1381,11 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only Part Sales results are shown; other entity groups are hidden.
+          <t>1. Only Part Sales results are shown; other entity groups are hidden.
 2. The 'Part Sales' tab appears selected/active.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 4 (Part Sales is a NEW searchable entity); 5.2 State 3, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 (Part Sales is a NEW searchable entity); 5.2 State 3, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1415,7 +1399,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Scoped tab shows the full result list with load-more; no Show-all link (v2)</t>
+          <t>Selecting a scope tab shows only that entity's results with its count</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1449,19 +1433,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In the All view each group shows up to 5 rows with a true total in its heading (for example "Work Orders (12)").
-2. There is NO "Show all N" link (dropped in v2, D15/FR-013).
-3. Clicking an entity's scope tab shows that entity's full result list (default 25) with cursor-based load-more inside the modal.
-4. No list-page banner is shown; the modal does not navigate to a filtered list page.
----
-This is the expected behaviour as per epic SV-9160 and story SV-9169 (scope tab strip) (D15) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-013), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+          <t>1. Selecting an entity scope tab scopes the query to that entity type only.
+2. Within the scoped tab the results carry that entity's true total count in the heading.
+3. When the scoped entity has more than five matches the same 'Show all N' link is available (full-page handoff per the Show-all case).
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 (scope tab scoping), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
+          <t>section 5.2 (scope tab scoping)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1470,2576 +1452,2515 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>The 'Contacts' tab shows only Contact results</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Scope Tabs</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1. Selecting the 'Contacts' tab scopes the query to contacts only.
+2. The tab carries the true contact count; results show contact rows only.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.2 (Contacts scope tab), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>section 5.2 (Contacts scope tab)</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>The 'Purchase Orders' tab shows only Purchase Order results</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Scope Tabs</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. Selecting the 'Purchase Orders' tab scopes the query to purchase orders only.
+2. The tab carries the true PO count; results show PO rows only (subject to permission).
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.2 (Purchase Orders scope tab), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>section 5.2 (Purchase Orders scope tab)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>The 'Vendor Invoices' tab shows only Vendor Invoice results</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Scope Tabs</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. Selecting the 'Vendor Invoices' tab scopes the query to vendor invoices only.
+2. The tab carries the true count; results show vendor-invoice rows only (subject to permission).
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.2 (Vendor Invoices scope tab), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>section 5.2 (Vendor Invoices scope tab)</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Each result group shows a heading with the total match count</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Grouped Results and Counts</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. Test data exists so a query (for example 'Fib') returns several Work Orders and a couple of Customers.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Type the query (for example 'Fib').
 2. Read each group heading.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Each group heading shows the entity name and the total count in parentheses, for example 'Work orders (12)' and 'Customers (2)'.
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1. Each group heading shows the entity name and the total count in parentheses, for example 'Work orders (12)' and 'Customers (2)'.
 2. The count reflects the total number of matches for that entity type, even when only the first few rows are shown.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3 (results grouped by entity type with a count), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3 (results grouped by entity type with a count), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.2 State 3 (results grouped by entity type with a count)</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>A group shows up to five results (raised from three)</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Grouped Results and Counts</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. Test data exists so at least one entity group has more than five matches (for example twelve Work Orders match 'Fib').</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Type the query so a group has many matches.
 2. Count the rows shown under that group heading in the 'All' view.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The group shows at most five result rows.
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. The group shows at most five result rows.
 2. It does not show six or more rows inline (the old behavior was three - it is now five).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 1 (old = 3 per category); 5.2 State 3 (up to 5 results), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 1 (old = 3 per category); 5.2 State 3 (up to 5 results), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>requirements.md 1 (old = 3 per category); 5.2 State 3 (up to 5 results)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>A 'Show all N' link appears when a group has more matches than are shown</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>A 'Show all N' link appears when a group has more than five matches</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Grouped Results and Counts</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A query returns more than five Work Order matches (for example twelve).</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Type the query.
 2. Look at the bottom of the Work Orders group.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. There is NO 'Show all N' link in v2 (dropped by D15/FR-013).
-2. In the All view a group shows up to 5 rows with its true total in the heading (for example 'Work Orders (12)').
-3. To see more than 5, the user opens that entity's scope tab (see the Scope Tabs cases).
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 3 ('Show all N work orders' link), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.2 State 3 ('Show all N work orders' link)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Show all N' switches the palette into that entity's scope tab</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1. When a result group has more than five matches, a 'Show all N' link appears to the right of that group's heading (for example 'Show all 12').
+2. A group with five or fewer matches shows no 'Show all' link.
+3. The number N reflects the true total for that entity in the current query, not the capped five.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 (Show all N link), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>section 5.2 (Show all N link)</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Show all N' hands off to the entity's list page with a banner</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Grouped Results and Counts</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open with a query showing a Work Orders group that has a 'Show all' link.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Click the 'Show all work orders' link.
 2. Watch the palette.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Opening an entity's scope tab (not a 'Show all' link, which no longer exists) shows that entity's full result list within the modal.
-2. The scoped list loads a default page (25) with cursor-based load-more inside the modal.
-3. The modal does not navigate away to a separate full page.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 (Show all switches to the scope tab - recommended); Open Question OQ-SPEC-1, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.2 (Show all switches to the scope tab - recommended); Open Question OQ-SPEC-1</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1. Clicking 'Show all N' closes the search modal and navigates to that entity's list page with the query carried over.
+2. The list is filtered to the query and a banner above the table reads 'Showing N &lt;entity&gt; matching «query»'.
+3. The banner has a 'Clear search' action that drops the filter and leaves the user on the unfiltered list.
+4. While the handoff filter is active, the list page's own inline search field stays empty so the two filters are not confused.
+5. This is implemented for Work Orders in the prototype; each remaining entity list is expected to get the same treatment.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 (Show all - full-page handoff and results banner), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>section 5.2 (Show all - full-page handoff and results banner)</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Groups appear in the fixed order Work Orders, Customers, Assets, Parts, Vendors, Part Sales</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Grouped Results and Counts</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A query matches all six entity types at once.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Type the query on the 'All' tab.
 2. Read the group headings top to bottom.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The groups appear top to bottom in this v2 nine-entity order: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. The groups appear top to bottom in this v2 nine-entity order: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
 2. The order does not change based on how many matches each group has.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 6.2 (group display order in 'All'), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.2 (group display order in 'All'), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>requirements.md 6.2 (group display order in 'All')</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>The typed text is highlighted inside each matching result</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Grouped Results and Counts</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. Test data exists such that 'Fib' matches records like 'S1-644 Fibridge Commercial'.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Type 'Fib'.
 2. Look at the matched part of the text in each result row.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The matched substring 'Fib' is visually highlighted (in the captures it is highlighted in yellow) inside the result's primary text.
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1. The matched substring 'Fib' is visually highlighted (in the captures it is highlighted in yellow) inside the result's primary text.
 2. Only the matched portion is highlighted, not the whole row.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.3 (matched substring highlighted), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 (matched substring highlighted), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.3 (matched substring highlighted)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>A screen reader announces the results count when it changes</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Grouped Results and Counts</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. A screen reader is turned on.
 2. The palette is open.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that returns results across several groups.
 2. Listen to the screen reader.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The screen reader announces the total results count when it changes, for example 'X results found across N categories'.
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. The screen reader announces the total results count when it changes, for example 'X results found across N categories'.
 2. Every interactive element (input, tabs, rows, links) has a visible focus ring when reached by keyboard.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 9 Non-Functional (screen-reader announcements when results count changes; focus rings), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 Non-Functional (screen-reader announcements when results count changes; focus rings), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>requirements.md 9 Non-Functional (screen-reader announcements when results count changes; focus rings)</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Group order follows the v2 nine-entity sequence; pinned top hit above groups</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Grouped Results and Counts</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in.
 2. A query matches across several of the nine entity types, and a query exists that is an exact ID match.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Search a broad term and read the group order in the All view.
 2. Search an exact identifier (score &gt; 0.95) and look above the groups.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Group display order in All is: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. Group display order in All is: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
 2. Within each group rows are sorted by score descending; ties break by recency.
 3. When the top result across all groups scores &gt; 0.95 (an ID match) it is pinned as a single row above the groups, carrying its entity icon.
 ---
-This is the expected behaviour as per epic SV-9160 and story SV-9165 (ranking engine) (D16) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-007), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>A Work Order result shows number, customer, status badge, assignee and date</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Per-Entity Result Shape</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A Work Order exists that matches the query (for example 'S1-644 Fibridge Commercial').</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that matches a Work Order.
 2. Read the Work Order result row.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The row shows the Work Order number and customer name as the main line (for example 'S1-644 Fibridge Commercial').
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1. The row shows the Work Order number and customer name as the main line (for example 'S1-644 Fibridge Commercial').
 2. A colored status badge is shown (for example Approved, Estimate).
 3. The lead technician / assignee name is shown (for example 'James Smith').
 4. A date is shown (for example 'Apr 27, 2026').
 5. A briefcase / work-order icon is shown on the left of the row.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 4 Work Orders (Displayed: WO number + customer, status badge, lead technician, asset/unit, date), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Work Orders (Displayed: WO number + customer, status badge, lead technician, asset/unit, date), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>requirements.md 4 Work Orders (Displayed: WO number + customer, status badge, lead technician, asset/unit, date)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>A Customer result shows name, address and an open work-order count chip</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Per-Entity Result Shape</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A Customer exists that matches the query (for example 'Fibridge Commercial').</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that matches a Customer.
 2. Read the Customer result row.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The row shows the customer name as the main line (for example 'Fibridge Commercial').
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1. The row shows the customer name as the main line (for example 'Fibridge Commercial').
 2. An address line is shown as the secondary line (for example '923 Ross Islands, X1T 2B1').
 3. A count chip is shown (the open work-order / document count, for example '12').
 4. A person icon is shown on the left of the row.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 4 Customers (Displayed: name, address line, open WO count badge, telephone on hover), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Customers (Displayed: name, address line, open WO count badge, telephone on hover), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>requirements.md 4 Customers (Displayed: name, address line, open WO count badge, telephone on hover)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>An Asset result shows year/make/model and the owning customer</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Per-Entity Result Shape</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. An Asset exists that matches the query (for example '2025 Freightliner M2' owned by 'Bryan Smith').</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that matches an Asset.
 2. Read the Asset result row.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The row shows year, make and model as the main line (for example '2025 Freightliner M2').
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1. The row shows year, make and model as the main line (for example '2025 Freightliner M2').
 2. The owning customer name is shown as smaller secondary text (for example 'Bryan Smith').
 3. A vehicle icon is shown on the left of the row.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 4 Assets (Displayed: year + make + model primary, customer name secondary), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Assets (Displayed: year + make + model primary, customer name secondary), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>requirements.md 4 Assets (Displayed: year + make + model primary, customer name secondary)</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>A Part result shows description, part number and a quantity chip colored by stock level</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Per-Entity Result Shape</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. Parts exist matching the query, including at least one in stock (green) and, if possible, one low (orange) and one out (red).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that matches parts (for example 'Microfiber' or a part number '65547').
 2. Read the Part result rows and the quantity chip color.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The row shows the part description as the main line (for example 'Microfiber' or 'Rear Shock').
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. The row shows the part description as the main line (for example 'Microfiber' or 'Rear Shock').
 2. The part number is shown as the secondary line (for example '65547').
 3. A total quantity chip is shown (for example '72').
 4. The quantity chip is colored by stock status: green when in stock, orange when low, red when out of stock.
 5. A tag / part icon is shown on the left of the row.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 4 Parts (Displayed: description, part number, total quantity with stock-status color), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Parts (Displayed: description, part number, total quantity with stock-status color), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>requirements.md 4 Parts (Displayed: description, part number, total quantity with stock-status color)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>A Vendor result shows the vendor name and address</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Per-Entity Result Shape</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A Vendor exists matching the query (for example 'Fibridge Mining').</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that matches a Vendor.
 2. Read the Vendor result row.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The row shows the vendor name as the main line (for example 'Fibridge Mining').
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1. The row shows the vendor name as the main line (for example 'Fibridge Mining').
 2. An address line is shown as the secondary line.
 3. A building icon is shown on the left of the row.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 4 Vendors (Displayed: vendor name primary, address line secondary), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Vendors (Displayed: vendor name primary, address line secondary), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>requirements.md 4 Vendors (Displayed: vendor name primary, address line secondary)</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>A Part Sale result shows the P-number, customer, status badge, total price and date</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Per-Entity Result Shape</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A Part Sale exists matching the query (for example 'P2-58' for 'Toboro Industries').</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that matches a Part Sale (for example 'P2-58').
 2. Read the Part Sale result row.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The row shows the P-number and customer name as the main line (for example 'P2-58 Toboro Industries').
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1. The row shows the P-number and customer name as the main line (for example 'P2-58 Toboro Industries').
 2. A status badge is shown.
 3. A total price and a created date are shown.
 4. A label icon is shown on the left of the row.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 4 Part Sales (Displayed: P-number + customer primary, status badge, total price + created date), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Part Sales (Displayed: P-number + customer primary, status badge, total price + created date), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>requirements.md 4 Part Sales (Displayed: P-number + customer primary, status badge, total price + created date)</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>A customer or vendor matched on a phone or email shows 'Contact/info match'</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>A customer or vendor matched on a contact field shows 'Contact match'</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Per-Entity Result Shape</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A customer exists whose telephone or email contains the query but whose name does not.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Type the customer's phone digits or email (a value that matches a contact field, not the name).
 2. Read the matched customer/vendor row's secondary line.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The customer/vendor still appears in the results.
-2. The secondary line shows 'Contact/info match' to indicate the match was on a contact field (phone/email) rather than the name.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 4 (secondary line shows 'Contact/info match'), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 4 (secondary line shows 'Contact/info match')</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1. The customer or vendor still appears in the results.
+2. Its secondary line shows 'Contact match' to indicate the match was on a contact field (phone or email) rather than the name.
+3. When the query reaches both a contact and its parent company, two rows are returned - the contact in the Contacts group and the company in its own group carrying the 'Contact match' label; neither row suppresses the other.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 (contact-field match), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>section 4 (contact-field match)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Work Order status badges use the correct colors</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Per-Entity Result Shape</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. Work Orders exist in several statuses (Approved, Estimate, In Progress, Review, Completed, Declined, Invoiced).</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Search so Work Orders in different statuses appear.
 2. Read the status badge colors.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Status badge colors match the Work Order list tokens: Approved green, Estimate blue, Review yellow, In Progress blue, Completed gray, Declined red, Invoiced purple.
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1. Status badge colors match the Work Order list tokens: Approved green, Estimate blue, Review yellow, In Progress blue, Completed gray, Declined red, Invoiced purple.
 2. Part stock badges use green (available), orange (low), red (out).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.3 (status badge colors, same tokens as the WO list), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 (status badge colors, same tokens as the WO list), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.3 (status badge colors, same tokens as the WO list)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>A misspelled name still finds the record - 'Petersn' finds 'Peterson'</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A record whose name contains 'Peterson' exists (for example a customer or vendor).</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Type the misspelled query 'Petersn' (missing the 'o').
 2. Read the results.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The 'Peterson' record is found and shown, despite the typo.
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1. The 'Peterson' record is found and shown, despite the typo.
 2. The matched part of the text is highlighted.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (token n-gram / trigram matching catches Petersn -&gt; Peterson), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (token n-gram / trigram matching catches Petersn -&gt; Peterson), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (token n-gram / trigram matching catches Petersn -&gt; Peterson)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>A misspelled name still finds the record - 'Abrige' finds 'Aabridge'</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A record whose name contains 'Aabridge' exists.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Type the misspelled query 'Abrige'.
 2. Read the results.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The 'Aabridge' record is found and shown, despite the typo.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 1 + 10 Phase 5 (fuzzy query 'Abrige'), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1. The 'Aabridge' record is found and shown, despite the typo.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 1 + 10 Phase 5 (fuzzy query 'Abrige'), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>requirements.md 1 + 10 Phase 5 (fuzzy query 'Abrige')</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>A transposed-letters query still finds the record - 'frieghtliner' finds 'Freightliner'</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. An asset or part whose text contains 'Freightliner' exists (for example '2025 Freightliner M2').</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Type the misspelled query 'frieghtliner' (letters transposed).
 2. Read the results.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The 'Freightliner' record is found and shown, despite the transposed letters.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (Damerau-Levenshtein; freihgtliner -&gt; freightliner), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1. The 'Freightliner' record is found and shown, despite the transposed letters.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (Damerau-Levenshtein; freihgtliner -&gt; freightliner), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (Damerau-Levenshtein; freihgtliner -&gt; freightliner)</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>A phonetically-similar name still finds the record - 'Filbridge' finds 'Fibridge'</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A customer/vendor/contact whose name contains 'Fibridge' exists.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Type the phonetically-similar query 'Filbridge'.
 2. Read the results.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The 'Fibridge' record is found and shown (matched by sound, as a last-resort phonetic match), likely lower in the ranking than an exact/near-exact match.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (phonetic fallback catches Filbridge -&gt; Fibridge), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1. The 'Fibridge' record is found and shown (matched by sound, as a last-resort phonetic match), likely lower in the ranking than an exact/near-exact match.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (phonetic fallback catches Filbridge -&gt; Fibridge), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (phonetic fallback catches Filbridge -&gt; Fibridge)</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>A Work Order number matches exactly with or without the dash or a space</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A Work Order 'S2-15276' exists.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Type 'S2-15276' and read the result.
 2. Clear the input and type 'S215276' (no dash) and read the result.
 3. Clear the input and type 'S2 15276' (with a space) and read the result.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. All three forms find the same Work Order 'S2-15276'.
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1. All three forms find the same Work Order 'S2-15276'.
 2. The Work Order number is treated as an identifier: it is normalized by stripping the dash/space, so 'S2-15276' equals 's215276'.
 3. The match is exact (identifier), not fuzzy.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (S2-15276 = s215276); identifier fields are exact-only, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (S2-15276 = s215276); identifier fields are exact-only, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (S2-15276 = s215276); identifier fields are exact-only</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>A VIN / serial number requires an exact match after normalization</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. An asset with a known VIN / serial number exists.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Type the asset's exact VIN / serial number and read the result.
 2. Clear the input, type the VIN with one wrong character, and read the result.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The exact VIN (case and spacing normalized) finds the matching asset / work order.
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1. The exact VIN (case and spacing normalized) finds the matching asset / work order.
 2. A VIN with a wrong character does NOT return a fuzzy match - VINs are exact-only identifiers, no typo tolerance.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>A telephone number matches on digits only, ignoring formatting</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A customer with telephone '(264) 328-6723' exists.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Type the digits '2643286723' and read the result.
 2. Clear the input, type '(264) 328-6723' with the formatting, and read the result.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Both forms find the same customer.
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1. Both forms find the same customer.
 2. The phone is normalized to digits only, so '(264) 328-6723' equals '2643286723'.
 3. The matched customer's secondary line shows 'Contact/info match' (matched on a contact field, not the name).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (phone normalization); 4 (Contact/info match affordance), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (phone normalization); 4 (Contact/info match affordance), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (phone normalization); 4 (Contact/info match affordance)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>A part number requires an exact match after normalization</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A part with a known part number (for example '65547') exists.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Type the exact part number '65547' and read the result.
 2. Clear the input, type a part number with one wrong digit, and read the result.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The exact part number finds the matching part.
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1. The exact part number finds the matching part.
 2. A part number with a wrong digit does NOT return a fuzzy match - part numbers are exact-only identifiers.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (What is NOT fuzzy: part number), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (What is NOT fuzzy: part number), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (What is NOT fuzzy: part number)</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Typos in identifier fields do NOT return fuzzy matches</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A Work Order 'S2-15276' exists and no Work Order 'S2-15286' exists.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Type a near-miss Work Order number, for example 'S2-15286' (one digit off from a real WO).
 2. Read the results.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The real Work Order 'S2-15276' is NOT returned as a fuzzy match.
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1. The real Work Order 'S2-15276' is NOT returned as a fuzzy match.
 2. Because identifier fields are exact-only, a one-digit-off WO number returns no fuzzy identifier match (it may show 'No results' if nothing else matches).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (exact identifier fields bypass fuzzy logic), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (exact identifier fields bypass fuzzy logic), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (exact identifier fields bypass fuzzy logic)</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>A soft (fuzzy) match is visually indicated</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A record exists that will only match via fuzzy logic (for example type 'Petersn' for a 'Peterson' record).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Type a fuzzy query (for example 'Petersn').
 2. Look at how the matched token is shown in the result row.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The matched token is highlighted.
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1. The matched token is highlighted.
 2. A subtle soft-match indicator is shown for fuzzy matches (spec mentions a '≈' symbol or italic treatment).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (fuzzy soft-match highlight treatment - design polish, confirm with design), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (fuzzy soft-match highlight treatment - design polish, confirm with design), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (fuzzy soft-match highlight treatment - design polish, confirm with design)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>A Part Sale P-number requires an exact match (no fuzzy typo tolerance)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Fuzzy Matching</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A Part Sale 'P2-58' exists and no Part Sale 'P2-59' exists.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Type the exact P-number 'P2-58' and read the result.
 2. Clear the input, type a near-miss P-number 'P2-59' (one digit off a real Part Sale), and read the results.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The exact P-number 'P2-58' finds the matching Part Sale.
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1. The exact P-number 'P2-58' finds the matching Part Sale.
 2. A one-digit-off P-number does NOT return the real Part Sale as a fuzzy match - P-numbers are exact-only identifiers, no typo tolerance (it may show 'No results' if nothing else matches).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>requirements.md 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization)</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>An exact identifier match is pinned as a single row at the very top</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Ranking and Prioritization</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A Work Order 'S2-15276' exists.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Type the exact Work Order number 'S2-15276'.
 2. Look at the top of the results.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The exactly-matched Work Order is pinned as a single row at the very top, above the grouped results, labeled with its entity icon.
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1. The exactly-matched Work Order is pinned as a single row at the very top, above the grouped results, labeled with its entity icon.
 2. This gives the 'type the number, jump straight to it' experience.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 6.2 (ID match &gt; 0.95 pinned at top), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.2 (ID match &gt; 0.95 pinned at top), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>requirements.md 6.2 (ID match &gt; 0.95 pinned at top)</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Within a group, more relevant results appear first</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Ranking and Prioritization</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. Several Work Orders match the query, some open/active (Approved, In Progress, Review) and recently updated, some old and Completed/Invoiced.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that matches many Work Orders.
 2. Read the order of the Work Order rows.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open/active and recently-updated Work Orders rank above old, closed ones.
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1. Open/active and recently-updated Work Orders rank above old, closed ones.
 2. Work Orders assigned to or recently viewed by the signed-in user are boosted; closed/Invoiced Work Orders older than 90 days are pushed down.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 6.1 Work Orders signals (open status +0.30, recency, assigned/viewed, old-closed demoted), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.1 Work Orders signals (open status +0.30, recency, assigned/viewed, old-closed demoted), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>requirements.md 6.1 Work Orders signals (open status +0.30, recency, assigned/viewed, old-closed demoted)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>In-stock parts rank above out-of-stock parts (out-of-stock not hidden)</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Ranking and Prioritization</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. Two parts match the query - one in stock, one out of stock.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Type a query that matches both parts.
 2. Read the order of the Part rows.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The in-stock part ranks above the out-of-stock part.
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1. The in-stock part ranks above the out-of-stock part.
 2. The out-of-stock part is still shown (out-of-stock parts are not demoted below relevance and are not hidden).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 6.1 Parts signals, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.1 Parts signals, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>requirements.md 6.1 Parts signals</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>On a Customer page, that customer's assets and work orders are boosted</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Ranking and Prioritization</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are on a specific Customer's page.
 2. That customer owns some assets and work orders, and other customers have similar-matching assets/work orders.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. While on the Customer page, open the palette and type a query that matches assets/work orders belonging to several customers.
 2. Read the ranking of the asset and work-order results.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Assets and Work Orders owned by the customer whose page you are on are boosted (appear higher) compared to the same search run from an unrelated page.
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. Assets and Work Orders owned by the customer whose page you are on are boosted (appear higher) compared to the same search run from an unrelated page.
 2. This is a lightweight, single contextual-bias signal.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 6.3 Contextual bias, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.3 Contextual bias, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>requirements.md 6.3 Contextual bias</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>On a Work Order page, parts already on that work order are pushed down</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Ranking and Prioritization</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are on a specific Work Order's page.
 2. That work order already has some parts on it, and other similar-matching parts exist that are not on it.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. While on the Work Order page, open the palette and search for parts.
 2. Read the ranking of the part results.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Parts already on that work order are pushed down (demoted) relative to other matching parts.
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1. Parts already on that work order are pushed down (demoted) relative to other matching parts.
 2. Other parts in the same category as the work order's existing parts get a small boost.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 6.3 Contextual bias, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.3 Contextual bias, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>requirements.md 6.3 Contextual bias</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>First-time empty state shows the placeholder, helper text and three quick-create buttons</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Orders rank by Ordered status and recency</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Ranking and Prioritization</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1. A Purchase Order that is still Ordered (not yet received) ranks above received ones.
+2. More recently created POs rank above older ones (recency decays over about two weeks).
+3. A PO created by the signed-in user gets a small additional boost.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 6.1 (Purchase Order signals), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>section 6.1 (Purchase Order signals)</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Vendor Invoices rank Unpaid first and by recency</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Ranking and Prioritization</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. An Unpaid vendor invoice ranks above paid ones.
+2. More recent invoice dates rank higher (recency decays over about a month).
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 6.1 (Vendor Invoice signals), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>section 6.1 (Vendor Invoice signals)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Contacts rank by open work, recent contact and primary status</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Ranking and Prioritization</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1. A contact whose owning company has at least one open work order ranks higher.
+2. A contact called or viewed by the signed-in user in the last 7 days gets a boost.
+3. A company's primary contact gets a small additional boost.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 6.1 (Contact signals), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>section 6.1 (Contact signals)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>First-time empty state shows the placeholder, helper text and quick-create buttons</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Empty and First-Time State</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with no recent search activity.
 2. The palette is open and the input is empty.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Open the palette without typing anything.
 2. Read the placeholder, the helper text, and the buttons.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The input shows the placeholder a plain search placeholder (no 'ask a question' / AI wording in v1 - exact copy per the v2 design).
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1. The modal input shows the placeholder 'Search work orders, customers, parts and more' (no 'ask a question' / AI wording - AI is out of scope in v1).
 2. Helper text below the input reads 'Type to start searching for work orders, parts, customers and more'.
 3. Three quick-create buttons are shown: 'New work order', 'New customer', 'New inventory part'.
-4. The footer keyboard legend is visible.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 1 (First-time search), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.2 State 1 (First-time search)</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+4. The footer keyboard legend is visible: down/up Navigate, Enter Select, Esc Close.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 / 5.2 (first-time state and placeholder copy), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>section 5.1 / 5.2 (first-time state and placeholder copy)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>The quick-create buttons in the empty state start the matching create flow</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Empty and First-Time State</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open in the empty state showing the three quick-create buttons.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New work order' and observe.
 2. Reopen the palette, click 'New customer' and observe.
 3. Reopen the palette, click 'New inventory part' and observe.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. 'New work order' starts the create-work-order flow.
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1. 'New work order' starts the create-work-order flow.
 2. 'New customer' starts the create-customer flow.
 3. 'New inventory part' starts the create-inventory-part flow.
 4. None of the buttons perform a destructive action.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 1 (quick-create chips), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 1 (quick-create chips), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.2 State 1 (quick-create chips)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Recent activity is grouped under Today, Yesterday, Past week and Past 30 days</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Recent Activity Default State</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user who has recently opened several records (across different days).
 2. The palette is open and the input is empty.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Open the palette without typing anything.
 2. Read the group headings and the rows under them.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Instead of the first-time helper text, the palette shows your recent activity.
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1. Instead of the first-time helper text, the palette shows your recent activity.
 2. Rows are grouped under time headings: 'Today', 'Yesterday', 'Past week', 'Past 30 days'.
 3. Each row is a previously opened record (not just a previous search word).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 2 (Recent searches grouped by interval); 8 (persist recent-entity-views 30 days), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 2 (Recent searches grouped by interval); 8 (persist recent-entity-views 30 days), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.2 State 2 (Recent searches grouped by interval); 8 (persist recent-entity-views 30 days)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Recent activity mixes different entity types using the same row template</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Recent Activity Default State</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You have recently opened records of different types (work orders, assets, customers, parts, part sales, vendors).
 2. The palette is open and empty.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Open the palette without typing.
 2. Read the recent rows across the time groups.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Recent rows include a mix of entity types (for example a Work Order, an Asset, a Customer, a Part, a Vendor).
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1. Recent rows include a mix of entity types (for example a Work Order, an Asset, a Customer, a Part, a Vendor).
 2. Each recent row uses the same row template as a normal result row (icon, primary line, secondary line, status/quantity cluster).
 3. Example rows: WO 'S1-644 Fisquare Farms' [Approved], Asset '2025 Freightliner M2 - Bryan Smith', Customer 'Adale Transport' with a doc chip, Part 'Rear Shock 65547' [72], Vendor 'Report Beverages'.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 2 (same row template as a result row), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 2 (same row template as a result row), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.2 State 2 (same row template as a result row)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Clicking a recent item opens that record</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Recent Activity Default State</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open and empty, showing recent activity.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Click a recent item (for example the Work Order 'S1-644 Fisquare Farms').
 2. Watch the screen.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The palette closes and the clicked record opens.
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1. The palette closes and the clicked record opens.
 2. Opening the record refreshes its position in recent activity (it is 'touched').
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 10 Phase 4 (records a touch on every result click / entity-page visit), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 4 (records a touch on every result click / entity-page visit), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>requirements.md 10 Phase 4 (records a touch on every result click / entity-page visit)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Clear all empties the history and returns to the first-time state</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Recent Activity Default State</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1. The first recent-activity group header carries a 'Clear all' action.
+2. Selecting 'Clear all' empties the entire recent-search history.
+3. After clearing, the panel falls back to the first-time state - helper text plus the three quick-create buttons - with no separate empty-history message.
+4. 'Clear all' is present on both web and mobile.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.2 / 5.6 / 8 (Clear all), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>section 5.2 / 5.6 / 8 (Clear all)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Recent-entities API records views and serves a deduped, permission-filtered list</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Recent Activity Default State</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in.
 2. You click search results and visit entity pages over several days.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Click a result and visit some entity pages directly.
 2. Reopen global search with an empty input and read the recent list.
 3. Re-view an earlier entity; delete an entity you had viewed.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Viewing an entity (a result click or a direct entity-page visit) records it via the recent-entities touch.
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. Viewing an entity (a result click or a direct entity-page visit) records it via the recent-entities touch.
 2. The empty-input recents list is per-user and per-tenant, retained 30 days, and is permission-filtered on read.
 3. The list is deduplicated: re-viewing an entity moves it to the top rather than adding a duplicate.
 4. A deleted entity is excluded from the recents list.
 ---
-This is the expected behaviour as per epic SV-9160 and story SV-9166 (recent-entities API) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-009), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>The typed query is retained in the header search field after the palette closes</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Persisting Query</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. You have typed a query (for example 'Fibridge') that returns results.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Type 'Fibridge' so results appear.
 2. Close the palette (press Esc or click a result).
 3. Look at the header search field.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. After closing, the header search field still shows the last query 'Fibridge' as plain text.
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1. After closing, the header search field still shows the last query 'Fibridge' as plain text.
 2. A small count badge (for example '1') is shown beside the persisted query.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 5 (Persisting search); 8 (persist last query, rehydrate on reopen), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 5 (Persisting search); 8 (persist last query, rehydrate on reopen), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.2 State 5 (Persisting search); 8 (persist last query, rehydrate on reopen)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Reopening the palette restores the last query, scope tab and result list</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Persisting Query</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. You have just searched (for example 'Fibridge'), selected a scope tab, and closed the palette (the query persists in the header field).</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Click the header search field again (or press Cmd+K).
 2. Look at the input, the scope tab, and the results.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The palette reopens with the last query 'Fibridge' already in the input.
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1. The palette reopens with the last query 'Fibridge' already in the input.
 2. The previously selected scope tab is restored.
 3. The result list for that query is shown again.
 4. The query text may appear selected/highlighted in the input so it can be replaced by typing.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 5 (Reopening restores the query, the scope tab, and the result list), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 5 (Reopening restores the query, the scope tab, and the result list), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.2 State 5 (Reopening restores the query, the scope tab, and the result list)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>The persisted query can be cleared with the clear (x) button</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Persisting Query</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open with a persisted query (for example 'Fibridge') in the input and a clear (x) button at the right of the input.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Click the clear (x) button at the right of the input.
 2. Look at the input and the results.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The input is cleared to empty.
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1. The input is cleared to empty.
 2. The results clear and the palette returns to the empty / recent-activity state (placeholder a plain search placeholder (no 'ask a question' / AI wording in v1 - exact copy per the v2 design)).
 3. The persisted query is removed from the header field.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 5; design-notes screenshot 9 (clearable via the x button), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 5; design-notes screenshot 9 (clearable via the x button), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.2 State 5; design-notes screenshot 9 (clearable via the x button)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>No matches shows 'No results for &lt;query&gt;' plus the three quick-create buttons</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>No matches shows 'No results for [query]' plus the three quick-create buttons</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>No-Results State</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. You will type a query that matches nothing (for example 'S1- 56438').</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Type a query with no matches (for example 'S1- 56438').
 2. Read the centered message and the buttons.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. A centered message reads 'No results for \'S1- 56438\'' (the exact query is echoed in quotes).
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1. A centered message reads 'No results for \'S1- 56438\'' (the exact query is echoed in quotes).
 2. The three quick-create buttons are shown: 'New work order', 'New customer', 'New inventory part'.
 3. The footer keyboard legend is still visible.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 4 (No results for &lt;query&gt; + quick-create chips), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.2 State 4 (No results for &lt;query&gt; + quick-create chips)</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 4 (No results for [query] + quick-create chips), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 5.2 State 4 (No results for [query] + quick-create chips)</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>A quick-create button in the no-results state starts the create flow</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>No-Results State</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. The palette is showing the no-results state with the three quick-create buttons.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New work order' (or 'New customer' / 'New inventory part').
 2. Watch the screen.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The matching create flow starts (create work order / customer / inventory part).
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1. The matching create flow starts (create work order / customer / inventory part).
 2. No destructive action occurs.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.2 State 4, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 4, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>requirements.md 5.2 State 4</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>Hovering a Work Order result shows an 'Add new line' action</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Hover Quick-Actions</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>1. The palette is open showing at least one Work Order row (in results or in recent activity).
-2. A pointer (mouse) is available.</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. Move the pointer over a Work Order row (for example 'S1-644 Fisquare Farms').
-2. Look at the right side of the row.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. A right-aligned 'Add new line' button appears on hover.
-2. The action is non-destructive.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.4 (Work Order -&gt; 'Add new line', only when currently editing a WO elsewhere), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.4 (Work Order -&gt; 'Add new line', only when currently editing a WO elsewhere)</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Hovering an Asset result shows 'New work order' plus history and checklist icons</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Hover Quick-Actions</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>1. The palette is open showing at least one Asset row.
-2. A pointer is available.</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>1. Move the pointer over an Asset row (for example '2025 Freightliner M2 - Fisquare Farms').
-2. Look at the right side of the row.</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. A 'New work order' button appears on hover.
-2. Two secondary icon buttons appear: a clock/history icon and a checklist/tasks icon.
-3. The actions are non-destructive.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.4 (Asset -&gt; 'New work order' + clock (history) and Invoice icons), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.4 (Asset -&gt; 'New work order' + clock (history) and Invoice icons)</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Hovering a Customer result shows 'New work order' (and 'New contact')</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Hover Quick-Actions</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>1. The palette is open showing at least one Customer row.
-2. A pointer is available.</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>1. Move the pointer over a Customer row (for example 'Adale Transport').
-2. Look at the right side of the row.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. A 'New work order' button appears on hover.
-2. A 'New contact' action is available for the customer (per spec).
-3. The actions are non-destructive.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.4 (Customer -&gt; 'New work order', 'New contact'), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.4 (Customer -&gt; 'New work order', 'New contact')</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Hovering a catalog part result shows 'Add part'</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Hover Quick-Actions</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>1. The palette is open showing a catalog part-style row.
-2. You are NOT currently editing a work order.
-3. A pointer is available.</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>1. Move the pointer over a catalog part row (for example 'P2-58 Toboro Industries').
-2. Look at the right side of the row.</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. On hover a Part quick action appears: "Add to work order" when you are currently editing a work order, otherwise "Add part".
-2. The Part row navigates to INVENTORY (not the catalogue).
-3. The action is non-destructive.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.4 (Part -&gt; 'Add part' when not currently editing a WO), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.4 (Part -&gt; 'Add part' when not currently editing a WO)</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Hovering a Vendor result shows 'Add contact'</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Hover Quick-Actions</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>1. The palette is open showing at least one Vendor row.
-2. A pointer is available.</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>1. Move the pointer over a Vendor row (for example 'Report Beverages').
-2. Look at the right side of the row.</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. An 'Add contact' button appears on hover.
-2. The action is non-destructive.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.4 (Vendor -&gt; 'Add contact'), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.4 (Vendor -&gt; 'Add contact')</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Hovering an inventory part while editing a work order shows 'Add to work order'</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Hover Quick-Actions</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>1. You are currently editing a work order.
-2. The palette is open showing an inventory part row (for example 'Rear Shock 65547' with a '72' quantity chip).
-3. A pointer is available.</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>1. Move the pointer over an inventory part row.
-2. Look at the right side of the row.</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. An 'Add to work order' button appears on hover.
-2. Using it adds the part to the work order you are editing (an inline add, non-destructive).
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.4 (Part -&gt; 'Add to work order' only when currently editing a WO), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.4 (Part -&gt; 'Add to work order' only when currently editing a WO)</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Hover quick-actions never trigger a destructive operation</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Hover Quick-Actions</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>1. The palette is open with rows across several entity types.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1. Hover each entity row type and review the available quick-action buttons.
-2. Note that every quick action is an add/create-style action.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. No quick action deletes, voids, or otherwise destroys data.
-2. Every action offered by a quick action is also reachable from the entity's full record (hover is non-essential).
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 5.4 (Quick actions never trigger destructive operations; hover state non-essential), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 5.4 (Quick actions never trigger destructive operations; hover state non-essential)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -4048,12 +3969,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Quick actions per entity include PO Receive and Part Sale Add part (v2)</t>
+          <t>Searching the in-page Work Orders list filters the list and shows a matching banner</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Hover Quick-Actions</t>
+          <t>In-Page Work Orders List Search</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4067,84 +3988,80 @@
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in on desktop (pointer present).
-2. Results exist across entity types; you can also be currently editing a work order.</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>1. Hover each entity row and read the quick action offered.
-2. Repeat while currently editing a work order.</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Quick actions by entity: Work Order -&gt; "Add new line" (only when currently editing a WO elsewhere); Customer and Contact -&gt; "New work order"; Asset -&gt; "New work order" plus history and invoices icon buttons; Part -&gt; "Add to work order" (when editing a WO) or "Add part"; Vendor -&gt; "Add contact"; Part Sale -&gt; "Add part"; Purchase Order -&gt; "Receive"; Vendor Invoice -&gt; none.
-2. No quick action is destructive, and every action is keyboard-reachable.
-3. The "currently editing a WO" state comes from the shared page-context source.
----
-This is the expected behaviour as per epic SV-9160 and story SV-9173 (quick actions) (D18) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-021), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>Searching the in-page Work Orders list filters the list and shows a matching banner</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>In-Page Work Orders List Search</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Work Orders list page (not the global search palette).
 2. Work Orders exist whose text contains 'Fib'.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Type 'Fib' into the in-page Work Orders list search field.
 2. Read the list and the banner above it.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The Work Orders list filters to only rows matching 'Fib'.
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1. The Work Orders list filters to only rows matching 'Fib'.
 2. A blue banner reads 'Showing 12 work orders matching \'Fib\'' (the count reflects the number of matches).
 3. A 'Clear search' link appears on the right of the banner.
 4. The list columns remain: On Site, Status, Number, Customer, Asset, Unit, VIN/Serial #, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total Price.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section design-notes screenshot 1 (in-page Work Orders list search banner), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), design-notes screenshot 1 (in-page Work Orders list search banner), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>design-notes screenshot 1 (in-page Work Orders list search banner)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>'Clear search' restores the full in-page Work Orders list</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>In-Page Work Orders List Search</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>1. The Work Orders list is filtered by an in-page search (banner 'Showing N work orders matching [q]' is visible).</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Click the 'Clear search' link in the banner.
+2. Read the list and the banner.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1. The filter is removed and the full Work Orders list is shown again.
+2. The 'Showing N work orders matching [q]' banner is removed.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), design-notes screenshot 1, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>design-notes screenshot 1 (in-page Work Orders list search banner)</t>
+          <t>design-notes screenshot 1</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -4153,101 +4070,100 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>'Clear search' restores the full in-page Work Orders list</t>
+          <t>A search failure shows the 'Search unavailable, retry' banner</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>In-Page Work Orders List Search</t>
+          <t>Error State</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>1. The Work Orders list is filtered by an in-page search (banner 'Showing N work orders matching &lt;q&gt;' is visible).</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>1. Click the 'Clear search' link in the banner.
-2. Read the list and the banner.</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The filter is removed and the full Work Orders list is shown again.
-2. The 'Showing N work orders matching &lt;q&gt;' banner is removed.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section design-notes screenshot 1, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>design-notes screenshot 1</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>A search failure shows the 'Search unavailable, retry' banner</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Error State</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. A network/backend failure of the search request can be simulated (for example offline the network or block the search endpoint).</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. With the search backend unreachable, type a query.
 2. Read the message shown in the palette.
 3. Restore connectivity and use the retry affordance.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. An inline banner reads 'Search unavailable, retry'.
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1. An inline banner reads 'Search unavailable, retry'.
 2. The palette degrades gracefully - it does not crash or show a blank screen.
 3. Retrying after connectivity is restored re-runs the search and shows results.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 8 (tolerate offline/network failures with an inline 'Search unavailable, retry' banner), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (tolerate offline/network failures with an inline 'Search unavailable, retry' banner), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 8 (tolerate offline/network failures with an inline 'Search unavailable, retry' banner)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>A user WITH Parts access sees Parts results in the palette</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Permissions and Role-Based Scoping</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as a user whose role includes Parts access.
+2. Parts exist that match the query.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the palette and type a query that matches parts.
+2. Read the results (on the 'All' tab and the 'Parts' tab).</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1. A 'Parts' group appears with matching part rows.
+2. The 'Parts' scope tab shows the part results.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (all result fields respect role-based-access checks), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>requirements.md 8 (tolerate offline/network failures with an inline 'Search unavailable, retry' banner)</t>
+          <t>requirements.md 9 (all result fields respect role-based-access checks)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4256,7 +4172,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>A user WITH Parts access sees Parts results in the palette</t>
+          <t>A technician WITHOUT Parts access does NOT see Parts results</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4266,39 +4182,39 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a user whose role includes Parts access.
-2. Parts exist that match the query.</t>
+          <t>1. You are signed in as a user whose role does NOT include Parts access.
+2. Parts exist that would match the query (verified visible to a Parts-enabled user).</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Open the palette and type a query that matches parts.
-2. Read the results (on the 'All' tab and the 'Parts' tab).</t>
+2. Read the results (on the 'All' tab and check the 'Parts' tab).</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A 'Parts' group appears with matching part rows.
-2. The 'Parts' scope tab shows the part results.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 9 (all result fields respect role-based-access checks), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+          <t>1. No 'Parts' group appears and no part rows are shown.
+2. The user cannot see part results they are not permitted to access, even though those parts exist.
+3. Results for entity types the user CAN access still appear normally.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (a technician without Parts access does not see Parts results), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>requirements.md 9 (all result fields respect role-based-access checks)</t>
+          <t>requirements.md 9 (a technician without Parts access does not see Parts results)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
@@ -4307,7 +4223,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>A technician WITHOUT Parts access does NOT see Parts results</t>
+          <t>A user WITHOUT Work Orders access does NOT see Work Order results</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4322,35 +4238,33 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a user whose role does NOT include Parts access.
-2. Parts exist that would match the query (verified visible to a Parts-enabled user).</t>
+          <t>1. You are signed in as a user whose role does NOT include Work Orders access.
+2. Work Orders exist that would match the query.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Open the palette and type a query that matches parts.
-2. Read the results (on the 'All' tab and check the 'Parts' tab).</t>
+          <t>1. Open the palette and type a query that matches Work Orders.
+2. Read the results (the 'All' tab and the 'Work Orders' tab).</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. No 'Parts' group appears and no part rows are shown.
-2. The user cannot see part results they are not permitted to access, even though those parts exist.
-3. Results for entity types the user CAN access still appear normally.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 9 (a technician without Parts access does not see Parts results), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+          <t>1. No 'Work orders' group appears and no Work Order rows are shown.
+2. Results for entity types the user CAN access still appear normally.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (all result fields respect role-based-access checks), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>requirements.md 9 (a technician without Parts access does not see Parts results)</t>
+          <t>requirements.md 9 (all result fields respect role-based-access checks)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4359,7 +4273,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>A user WITHOUT Work Orders access does NOT see Work Order results</t>
+          <t>Results are limited to the signed-in user's own tenant</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4369,7 +4283,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4379,29 +4293,28 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a user whose role does NOT include Work Orders access.
-2. Work Orders exist that would match the query.</t>
+          <t>1. You are signed in to one tenant/organization.
+2. Records with the same searchable text exist under a different tenant.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>1. Open the palette and type a query that matches Work Orders.
-2. Read the results (the 'All' tab and the 'Work Orders' tab).</t>
+          <t>1. Open the palette and type a query.
+2. Read the results.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. No 'Work orders' group appears and no Work Order rows are shown.
-2. Results for entity types the user CAN access still appear normally.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 9 (all result fields respect role-based-access checks), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+          <t>1. Only records belonging to your own tenant/organization are returned.
+2. No records from any other tenant are shown (tenant isolation is respected).
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (all result fields respect existing tenant-isolation checks), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>requirements.md 9 (all result fields respect role-based-access checks)</t>
+          <t>requirements.md 9 (all result fields respect existing tenant-isolation checks)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4410,7 +4323,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Results are limited to the signed-in user's own tenant</t>
+          <t>An entity type with no accessible records shows no group (and its scope tab shows the empty state)</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4425,141 +4338,139 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in to one tenant/organization.
-2. Records with the same searchable text exist under a different tenant.</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the palette and type a query.
-2. Read the results.</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Only records belonging to your own tenant/organization are returned.
-2. No records from any other tenant are shown (tenant isolation is respected).
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 9 (all result fields respect existing tenant-isolation checks), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 9 (all result fields respect existing tenant-isolation checks)</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>An entity type with no accessible records shows no group (and its scope tab shows the empty state)</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Permissions and Role-Based Scoping</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user who has zero accessible records of one entity type (for example the tenant has no Part Sales yet, or the user's role scopes an entity type down to no records).
 2. Other entity types do have matching records for the query.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Open the palette and type a query on the 'All' tab.
 2. Read the grouped results and confirm the empty entity type has no group.
 3. Open the scope tab for the empty entity type (for example the 'Part Sales' tab).</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. On the 'All' tab, no group appears for the entity type that has zero accessible results (the empty group is simply not shown).
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1. On the 'All' tab, no group appears for the entity type that has zero accessible results (the empty group is simply not shown).
 2. Groups for the entity types that do have matches still appear normally.
 3. The empty entity type's scope tab shows its empty / no-results treatment rather than an error.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 9 (must work for a single-tenant dataset where any entity type is empty, e.g. no part sales yet), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (must work for a single-tenant dataset where any entity type is empty, e.g. no part sales yet), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>requirements.md 9 (must work for a single-tenant dataset where any entity type is empty, e.g. no part sales yet)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Nine-entity permission bundles hide rows and counts; price fields masked</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Permissions and Role-Based Scoping</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. You can sign in as roles with different view bundles, and as one without See Financial Data, and as TimeClock.
 2. Results exist across all nine entity types.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. As a role missing a bundle (e.g. no Vendor &amp; Order Management), search and check POs/Vendor Invoices/Vendors.
 2. As a user without See Financial Data, check price fields.
 3. As TimeClock, search anything.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Permission filtering follows the 9-entity bundle mapping: work_orders-&gt;Work Orders: View; part_sales-&gt;Part Sales: View; customers/contacts/assets-&gt;Customers: View; parts-&gt;Catalog &amp; Inventory: View; vendors/purchase_orders/vendor_invoices-&gt;Vendor &amp; Order Management: View.
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1. Permission filtering follows the 9-entity bundle mapping: work_orders-&gt;Work Orders: View; part_sales-&gt;Part Sales: View; customers/contacts/assets-&gt;Customers: View; parts-&gt;Catalog &amp; Inventory: View; vendors/purchase_orders/vendor_invoices-&gt;Vendor &amp; Order Management: View.
 2. A hidden entity group leaks neither rows nor its count, and no scope tab appears for it.
 3. Without See Financial Data every price field is masked in results (part purchase/sell price, part-sale total, WO total, PO total, vendor-invoice total); masked values are never sent in the response.
 4. The TimeClock role gets an empty result set.
 ---
-This is the expected behaviour as per epic SV-9160 and story SV-9162 (BE search endpoint) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (NFR-003, NFR-004, NFR-005), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/search returns grouped results for scope=all</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>API — Global Search Endpoint</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1. You can call the backend search endpoint with a valid session.
+2. Test data exists so a query matches multiple entity types.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1. Send GET /api/search with q set to the query and scope set to 'all'.
+2. Inspect the HTTP status and the response body.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1. The response returns HTTP 200.
+2. The body is a grouped, ranked, scored payload containing groups for the matching entity types.
+3. Each group includes the per-item metadata needed to render rows without extra fetches.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 1 (GET /api/search; scope=all), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
+          <t>requirements.md 10 Phase 1 (GET /api/search; scope=all)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4568,7 +4479,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GET /api/search returns grouped results for scope=all</t>
+          <t>The scope parameter restricts GET /api/search to a single entity type</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4583,174 +4494,120 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>1. You can call the backend search endpoint with a valid session.
-2. Test data exists so a query matches multiple entity types.</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>1. Send GET /api/search with q set to the query and scope set to 'all'.
-2. Inspect the HTTP status and the response body.</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The response returns HTTP 200.
-2. The body is a grouped, ranked, scored payload containing groups for the matching entity types.
-3. Each group includes the per-item metadata needed to render rows without extra fetches.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 10 Phase 1 (GET /api/search; scope=all), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 10 Phase 1 (GET /api/search; scope=all)</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>The scope parameter restricts GET /api/search to a single entity type</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>API — Global Search Endpoint</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You can call the backend search endpoint.
 2. A query matches multiple entity types.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Send GET /api/search with q set and scope set to 'work_orders'.
 2. Inspect the response.
 3. Repeat with scope set to each of 'customers', 'assets', 'parts', 'vendors', 'part_sales'.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Each call returns HTTP 200.
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1. Each call returns HTTP 200.
 2. Each response contains results only for the requested scope's entity type.
 3. The accepted scope values are all, work_orders, customers, assets, parts, vendors, part_sales.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 10 Phase 1 (scope parameter), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 1 (scope parameter), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>requirements.md 10 Phase 1 (scope parameter)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>GET /api/search caps each group at the limit (default 5) and returns per-group totals</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>API — Global Search Endpoint</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. You can call the backend search endpoint.
 2. A query matches more than five records of one entity type (for example twelve Work Orders).</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Send GET /api/search with q set and no limit parameter.
 2. Inspect the number of rows returned for the over-full group and the total field.
 3. Repeat with limit set to a smaller value (for example 3).</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. With no limit, each group returns at most 5 rows (the default per-group cap).
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1. With no limit, each group returns at most 5 rows (the default per-group cap).
 2. Each group reports its full total count (for example total 12) even though only 5 rows are returned.
 3. Setting limit changes the per-group cap accordingly.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 10 Phase 1 (limit default 5; response includes per-group totals), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 1 (limit default 5; response includes per-group totals), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>requirements.md 10 Phase 1 (limit default 5; response includes per-group totals)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>GET /api/search matches identifier fields exactly after normalization</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>API — Global Search Endpoint</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. You can call the backend search endpoint.
 2. A Work Order 'S2-15276' exists.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Send GET /api/search with q set to 'S2-15276'.
 2. Send GET /api/search with q set to 's215276' (no dash).
@@ -4758,20 +4615,69 @@
 4. Compare the matched Work Order in each response.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. All three requests return HTTP 200 and match the same Work Order 'S2-15276'.
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1. All three requests return HTTP 200 and match the same Work Order 'S2-15276'.
 2. The identifier is normalized (case, diacritics, non-alphanumerics stripped) before matching.
 3. The exact-match result scores high enough to be flagged as the pinned top match (score above 0.95).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (identifier normalization); 6.2 (ID match pinned), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (identifier normalization); 6.2 (ID match pinned), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 7 (identifier normalization); 6.2 (ID match pinned)</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/search does NOT apply fuzzy matching to identifier fields</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>API — Global Search Endpoint</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1. You can call the backend search endpoint.
+2. A Work Order 'S2-15276' exists and 'S2-15286' does not.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1. Send GET /api/search with q set to 'S2-15286' (one digit off a real WO number).
+2. Inspect the response for a Work Order match.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1. The real Work Order 'S2-15276' is NOT returned as a fuzzy identifier match.
+2. Identifier fields (VIN, WO number, P-number, part number) require exact match after normalization; fuzzy logic is bypassed for them.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (What is NOT fuzzy), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>requirements.md 7 (identifier normalization); 6.2 (ID match pinned)</t>
+          <t>requirements.md 7 (What is NOT fuzzy)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4780,7 +4686,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GET /api/search does NOT apply fuzzy matching to identifier fields</t>
+          <t>GET /api/search enforces role-based access on the server (no forbidden entity results)</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4795,140 +4701,138 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>1. You can call the backend search endpoint.
-2. A Work Order 'S2-15276' exists and 'S2-15286' does not.</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>1. Send GET /api/search with q set to 'S2-15286' (one digit off a real WO number).
-2. Inspect the response for a Work Order match.</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The real Work Order 'S2-15276' is NOT returned as a fuzzy identifier match.
-2. Identifier fields (VIN, WO number, P-number, part number) require exact match after normalization; fuzzy logic is bypassed for them.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 7 (What is NOT fuzzy), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 7 (What is NOT fuzzy)</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>GET /api/search enforces role-based access on the server (no forbidden entity results)</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>API — Global Search Endpoint</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You can call the backend search endpoint as a user whose role does NOT include Parts access.
 2. Parts exist that match the query.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Send GET /api/search with q set to a query that matches parts, and scope set to 'all'.
 2. Inspect the response for a parts group.
 3. Send GET /api/search with scope set to 'parts' as the same restricted user.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The response contains no parts results for the restricted user (permission filtering is enforced server-side, not just hidden in the UI).
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1. The response contains no parts results for the restricted user (permission filtering is enforced server-side, not just hidden in the UI).
 2. Scoping directly to 'parts' still returns no forbidden parts (empty or a permission-appropriate response).
 3. Entity types the user is allowed to access are still returned.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 9 (results respect role-based-access checks - enforced server-side), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (results respect role-based-access checks - enforced server-side), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>requirements.md 9 (results respect role-based-access checks - enforced server-side)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>GET /api/search returns an error response the UI can degrade on</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>API — Global Search Endpoint</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. You can call the backend search endpoint.
 2. You can force an error condition (for example an invalid scope value, or a backend/search-infra failure).</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Send GET /api/search with an invalid parameter (for example an unknown scope value).
 2. Inspect the HTTP status and error body.
 3. Separately, simulate a backend/search failure and observe the response.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. An invalid request returns an appropriate 4xx status with an error body.
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1. An invalid request returns an appropriate 4xx status with an error body.
 2. A backend failure returns a 5xx or error payload that the frontend maps to the inline 'Search unavailable, retry' banner.
 3. The endpoint fails gracefully rather than returning malformed data.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 8 (offline/network failure handling), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (offline/network failure handling), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 8 (offline/network failure handling)</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/search groups results in the fixed group order with ranking metadata</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>API — Global Search Endpoint</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>1. You can call the backend search endpoint.
+2. A query matches all six entity types.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Send GET /api/search with q set and scope set to 'all'.
+2. Inspect the order of the groups and the per-item score/rank fields in the response.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1. Groups are returned in the v2 nine-entity order: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
+2. Within each group items are ordered by score descending; ties break by recency.
+3. Each item carries the metadata needed to render its row (entity type, primary/secondary fields, badges/quantity, score) without extra fetches, and true per-group totals.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.2 (group order); 10 Phase 1 (per-item metadata), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>requirements.md 8 (offline/network failure handling)</t>
+          <t>requirements.md 6.2 (group order); 10 Phase 1 (per-item metadata)</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
@@ -4937,7 +4841,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GET /api/search groups results in the fixed group order with ranking metadata</t>
+          <t>GET /api/search supports cursor pagination for a scoped tab</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4956,84 +4860,82 @@
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>1. You can call the backend search endpoint.
-2. A query matches all six entity types.</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>1. Send GET /api/search with q set and scope set to 'all'.
-2. Inspect the order of the groups and the per-item score/rank fields in the response.</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Groups are returned in the v2 nine-entity order: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
-2. Within each group items are ordered by score descending; ties break by recency.
-3. Each item carries the metadata needed to render its row (entity type, primary/secondary fields, badges/quantity, score) without extra fetches, and true per-group totals.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 6.2 (group order); 10 Phase 1 (per-item metadata), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 6.2 (group order); 10 Phase 1 (per-item metadata)</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>GET /api/search supports cursor pagination for a scoped tab</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>API — Global Search Endpoint</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. You can call the backend search endpoint.
 2. A query matches many records of one entity type (more than one page).</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Send GET /api/search with q set, scope set to a single entity type, and a limit.
 2. Take the cursor from the response and send GET /api/search again with that cursor.
 3. Compare the two pages of results.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The first response returns the first page plus a cursor.
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1. The first response returns the first page plus a cursor.
 2. Passing the cursor returns the next page of scoped results (no duplicates, no gaps).
 3. Pagination applies to the scoped-tab view.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 10 Phase 1 (cursor parameter), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 1 (cursor parameter), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 10 Phase 1 (cursor parameter)</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>The context parameter biases GET /api/search ranking to the current page</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>API — Global Search Endpoint</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>1. You can call the backend search endpoint.
+2. A specific customer owns some assets/work orders; other customers have similar matches.</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. Send GET /api/search with q set and no context, and note the ranking of assets/work orders.
+2. Send GET /api/search with q set and context set to {type: customer, id: [that customer]}.
+3. Compare the rankings.</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1. With the customer context, assets and work orders owned by that customer are boosted in the ranking versus the no-context call.
+2. The context parameter takes an optional {type, id} for page-context bias.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.3 (contextual bias); 10 Phase 1 (context parameter), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>requirements.md 10 Phase 1 (cursor parameter)</t>
+          <t>requirements.md 6.3 (contextual bias); 10 Phase 1 (context parameter)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -5042,7 +4944,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>The context parameter biases GET /api/search ranking to the current page</t>
+          <t>Recent-entities endpoints record and return recent activity</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5062,235 +4964,230 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>1. You can call the backend search endpoint.
-2. A specific customer owns some assets/work orders; other customers have similar matches.</t>
+          <t>1. You can call the recent-entities endpoints with a valid session.</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>1. Send GET /api/search with q set and no context, and note the ranking of assets/work orders.
-2. Send GET /api/search with q set and context set to {type: customer, id: &lt;that customer&gt;}.
-3. Compare the rankings.</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. With the customer context, assets and work orders owned by that customer are boosted in the ranking versus the no-context call.
-2. The context parameter takes an optional {type, id} for page-context bias.
----
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 6.3 (contextual bias); 10 Phase 1 (context parameter), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md 6.3 (contextual bias); 10 Phase 1 (context parameter)</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Recent-entities endpoints record and return recent activity</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>API — Global Search Endpoint</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>1. You can call the recent-entities endpoints with a valid session.</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Send POST /user/recent-entities/touch for a record (for example a work order you opened).
 2. Send GET /user/recent-entities.
 3. Inspect the returned list and its time bucketing.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. POST /user/recent-entities/touch records the touch (HTTP 2xx).
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /user/recent-entities/touch records the touch (HTTP 2xx).
 2. GET /user/recent-entities returns the recently touched records, retained for 30 days.
 3. The results support bucketing into Today / Yesterday / Past week / Past 30 days at render time.
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 8 (persist recent-entity-views 30 days); 10 Phase 4, read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (persist recent-entity-views 30 days); 10 Phase 4, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>requirements.md 8 (persist recent-entity-views 30 days); 10 Phase 4</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Search input is debounced before the backend is queried</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>API — Global Search Endpoint</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. The palette is open.
 2. You can observe outgoing search requests (for example via browser network tools).</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Type a multi-character query quickly without pausing.
 2. Observe how many GET /api/search calls are sent while typing.
 3. Pause typing and observe.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The backend is not queried on every keystroke; input is debounced (about 150ms) so a request fires after a short pause.
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1. The backend is not queried on every keystroke; input is debounced (about 150ms) so a request fires after a short pause.
 2. Grouped results render quickly once the response arrives (target within about 200ms at p95).
 ---
-This is the expected behaviour as per the Global Search PRD (Confluence page 576978945), section 8 (debounce input at 150ms; render within 200ms p95), read on 16 July 2026, and epic SV-9160, read on 21 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (debounce input at 150ms; render within 200ms p95), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>requirements.md 8 (debounce input at 150ms; render within 200ms p95)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Contacts are a searchable entity with their own result row and tab</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Contacts Entity (v2)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Customers access.
 2. Contacts exist that belong to companies (company-less contacts are excluded from the index).</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Open global search and type a contact's name or phone/email.
 2. Look at the Contacts group and the scope tabs.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Contacts appear as their own searchable entity (one of the nine v2 entity types), grouped under a "Contacts" heading with a true count.
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1. Contacts appear as their own searchable entity (one of the nine v2 entity types), grouped under a "Contacts" heading with a true count.
 2. A Contacts scope tab is offered (subject to permission).
 3. A contact row carries the contact (user-round) icon, the contact name (primary), and its company/context (secondary); a match on phone/email carries the "Contact/info match" flag.
 4. Company-less contacts (no company_id) are not indexed and do not appear.
 ---
-This is the expected behaviour as per epic SV-9160 and story SV-9162 (BE search endpoint) / SV-9170 (result rows) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-002, FR-014, NFR-003), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>WO, Inventory Parts and Customers list search served by the unified engine</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Page-Search Cutover (v2)</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in.
 2. The Work Orders, Inventory Parts and Customers list pages are reachable.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Orders list page, use its in-page search and compare results to the old behaviour.
 2. Repeat on the Inventory Parts list and the Customers list.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The in-page list search on the Work Orders, Inventory Parts and Customers pages is served by the same unified search engine, with identical matching (normalisation, identifier parsing, fuzzy) to global search.
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>1. The in-page list search on the Work Orders, Inventory Parts and Customers pages is served by the same unified search engine, with identical matching (normalisation, identifier parsing, fuzzy) to global search.
 2. Results respect the same tenant isolation and permission rules as global search.
 3. Adding a new searchable entity is a single provider class plus mapping (framework extensibility), so page and global search stay in lockstep.
 4. Exports keep their current data path in v1 (not cut over).
 ---
-This is the expected behaviour as per epic SV-9160 and story SV-9306 (page-search cutover) / SV-9162 (framework) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-018 (Phase 5)), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Old global-search path is removed on direct rollout (no Global Search feature)</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Page-Search Cutover (v2)</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in after the v2 rollout.
+2. No Global Search feature gates the feature.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1. Use global search and the cut-over list pages.
+2. Confirm the old dropdown path is gone.</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1. Global Search v2 ships for everyone with no Global Search feature.
+2. The old GET /api/global-search/fetch endpoint, its handler and the client-side filtering are removed after stabilisation.
+3. The 3-result-per-category dropdown behaviour is replaced entirely by the modal.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5304,12 +5201,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Old global-search path is removed on direct rollout (no Global Search feature)</t>
+          <t>Hovering a Work Order result shows an 'Add new line' action</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Page-Search Cutover (v2)</t>
+          <t>Global Search - Out of V1 Scope (not tested this release)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5324,30 +5221,29 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in after the v2 rollout.
-2. No Global Search feature gates the feature.</t>
+          <t>1. The palette is open showing at least one Work Order row (in results or in recent activity).
+2. A pointer (mouse) is available.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1. Use global search and the cut-over list pages.
-2. Confirm the old dropdown path is gone.</t>
+          <t>1. Move the pointer over a Work Order row (for example 'S1-644 Fisquare Farms').
+2. Look at the right side of the row.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Global Search v2 ships for everyone with no Global Search feature.
-2. The old GET /api/global-search/fetch endpoint, its handler and the client-side filtering are removed after stabilisation.
-3. The 3-result-per-category dropdown behaviour is replaced entirely by the modal.
----
-This is the expected behaviour as per epic SV-9160 and story SV-9176 (rollout) (D10) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-019), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
+          <t>1. A right-aligned 'Add new line' button appears on hover.
+2. The action is non-destructive.
+---
+EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Work Order -&gt; 'Add new line', only when currently editing a WO elsewhere), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
+          <t>requirements.md 5.4 (Work Order -&gt; 'Add new line', only when currently editing a WO elsewhere)</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5356,162 +5252,765 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>Hovering an Asset result shows 'New work order' plus history and checklist icons</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Global Search - Out of V1 Scope (not tested this release)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1. The palette is open showing at least one Asset row.
+2. A pointer is available.</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1. Move the pointer over an Asset row (for example '2025 Freightliner M2 - Fisquare Farms').
+2. Look at the right side of the row.</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>1. A 'New work order' button appears on hover.
+2. Two secondary icon buttons appear: a clock/history icon and a checklist/tasks icon.
+3. The actions are non-destructive.
+---
+EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Asset -&gt; 'New work order' + clock (history) and Invoice icons), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 5.4 (Asset -&gt; 'New work order' + clock (history) and Invoice icons)</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Hovering a Customer result shows 'New work order' (and 'New contact')</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Global Search - Out of V1 Scope (not tested this release)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1. The palette is open showing at least one Customer row.
+2. A pointer is available.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>1. Move the pointer over a Customer row (for example 'Adale Transport').
+2. Look at the right side of the row.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1. A 'New work order' button appears on hover.
+2. A 'New contact' action is available for the customer (per spec).
+3. The actions are non-destructive.
+---
+EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Customer -&gt; 'New work order', 'New contact'), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 5.4 (Customer -&gt; 'New work order', 'New contact')</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Hovering a catalog part result shows 'Add part'</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Global Search - Out of V1 Scope (not tested this release)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1. The palette is open showing a catalog part-style row.
+2. You are NOT currently editing a work order.
+3. A pointer is available.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1. Move the pointer over a catalog part row (for example 'P2-58 Toboro Industries').
+2. Look at the right side of the row.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1. On hover a Part quick action appears: "Add to work order" when you are currently editing a work order, otherwise "Add part".
+2. The Part row navigates to INVENTORY (not the catalogue).
+3. The action is non-destructive.
+---
+EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Part -&gt; 'Add part' when not currently editing a WO), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 5.4 (Part -&gt; 'Add part' when not currently editing a WO)</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Hovering a Vendor result shows 'Add contact'</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Global Search - Out of V1 Scope (not tested this release)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>1. The palette is open showing at least one Vendor row.
+2. A pointer is available.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1. Move the pointer over a Vendor row (for example 'Report Beverages').
+2. Look at the right side of the row.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1. An 'Add contact' button appears on hover.
+2. The action is non-destructive.
+---
+EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Vendor -&gt; 'Add contact'), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 5.4 (Vendor -&gt; 'Add contact')</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Hovering an inventory part while editing a work order shows 'Add to work order'</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Global Search - Out of V1 Scope (not tested this release)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1. You are currently editing a work order.
+2. The palette is open showing an inventory part row (for example 'Rear Shock 65547' with a '72' quantity chip).
+3. A pointer is available.</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. Move the pointer over an inventory part row.
+2. Look at the right side of the row.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1. An 'Add to work order' button appears on hover.
+2. Using it adds the part to the work order you are editing (an inline add, non-destructive).
+---
+EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Part -&gt; 'Add to work order' only when currently editing a WO), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 5.4 (Part -&gt; 'Add to work order' only when currently editing a WO)</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Hover quick-actions never trigger a destructive operation</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Global Search - Out of V1 Scope (not tested this release)</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>1. The palette is open with rows across several entity types.</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. Hover each entity row type and review the available quick-action buttons.
+2. Note that every quick action is an add/create-style action.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1. No quick action deletes, voids, or otherwise destroys data.
+2. Every action offered by a quick action is also reachable from the entity's full record (hover is non-essential).
+---
+EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Quick actions never trigger destructive operations; hover state non-essential), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md 5.4 (Quick actions never trigger destructive operations; hover state non-essential)</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Quick actions per entity include PO Receive and Part Sale Add part (v2)</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Global Search - Out of V1 Scope (not tested this release)</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in on desktop (pointer present).
+2. Results exist across entity types; you can also be currently editing a work order.</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. Hover each entity row and read the quick action offered.
+2. Repeat while currently editing a work order.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1. Quick actions by entity: Work Order -&gt; "Add new line" (only when currently editing a WO elsewhere); Customer and Contact -&gt; "New work order"; Asset -&gt; "New work order" plus history and invoices icon buttons; Part -&gt; "Add to work order" (when editing a WO) or "Add part"; Vendor -&gt; "Add contact"; Part Sale -&gt; "Add part"; Purchase Order -&gt; "Receive"; Vendor Invoice -&gt; none.
+2. No quick action is destructive, and every action is keyboard-reachable.
+3. The "currently editing a WO" state comes from the shared page-context source.
+---
+EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
           <t>Global search works on mobile/tablet viewports per the mobile design</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Mobile Global Search (v2)</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in on a mobile or tablet viewport (below Quasar's sm breakpoint).
 2. The mobile Global Search design is available.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Open global search on a phone.
 2. Type a query and browse grouped results and scope tabs.
 3. Try to reach a row's quick action.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The global search surface is usable on mobile/tablet viewports, matching the Mobile Global Search design.
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1. The global search surface is usable on mobile/tablet viewports, matching the Mobile Global Search design.
 2. Results, grouping, scope tabs and keyboard/entity behaviour remain reachable without horizontal scroll.
 3. Quick actions remain reachable on touch (no hover) via the design's touch affordance.
 4. The tab strip remains usable with up to ten tabs on a narrow viewport.
 ---
-This is the expected behaviour as per epic SV-9160 and story SV-9168 (modal shell) / SV-9169 (tab strip) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-022), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>On mobile the search is a full-screen surface with a Cancel action</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Global Search (v2)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1. On a phone the search is a full-screen screen that replaces the page, not a centered modal.
+2. The top bar shows a 'Cancel' action next to the input.
+3. The placeholder copy is 'Search everything'.
+4. There is no keyboard-hints footer on mobile.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile surface), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>section 5.6 (mobile surface)</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>On mobile the scope chip row appears only with a query and lists matched types</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Global Search (v2)</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1. Scope selection on mobile is a horizontal chip row.
+2. The chip row appears only once there is a query.
+3. It lists only the entity types that actually matched, each with its count, so the row stays short.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile scope chips), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>section 5.6 (mobile scope chips)</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>On mobile results are uncapped and scroll with sticky group headers</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Global Search (v2)</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1. Results are not capped per group and there is no 'Show all' overflow on mobile.
+2. The user scrolls the full grouped list.
+3. Group headers stick to the top of the list while scrolling.
+4. A tap on a row opens the record.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile results), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>section 5.6 (mobile results)</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Mobile first-time, recent and no-results states match web with stacked buttons</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Global Search (v2)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1. The first-time, recent-searches and no-results states match the web states.
+2. The quick-create buttons are stacked full-width instead of inline.
+3. 'Clear all' behaves as on web: clearing the history returns the screen to the first-time state.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile states), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>section 5.6 (mobile states)</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>On mobile the full-page handoff and keyboard navigation do not apply</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Mobile Global Search (v2)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available to the signed-in user.</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Perform the action described and observe the result.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1. The full-page result handoff and its banner (the web 'Show all' behaviour) do not apply on mobile in v1 - the mobile lists have no query handoff.
+2. Keyboard navigation does not apply on mobile.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile deferrals), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>section 5.6 (mobile deferrals)</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Purchase Orders searchable; real number format; Receive quick action</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Purchase Orders Entity (v2)</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Vendor &amp; Order Management access.
 2. Purchase orders exist.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Open global search and type a PO number or vendor.
 2. Look at the Purchase Orders group, the row, and the hover quick action.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Purchase Orders appear as their own searchable entity, grouped under a "Purchase Orders" heading with a true count and a scope tab (subject to permission).
-2. A PO row carries the package icon and the PO number in the real spliced format (for example "S12-1234" via formatWorkOrderId).
-3. On hover the PO row offers a "Receive" quick action (never destructive).
-4. PO results are gated by Vendor &amp; Order Management: View.
----
-This is the expected behaviour as per epic SV-9160 and story SV-9162 (BE search endpoint) / SV-9173 (quick actions) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-002, FR-021 (D18), NFR-004), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>1. Purchase Orders appear as their own searchable entity, grouped under a 'Purchase Orders' heading with a true count and a scope tab (subject to permission).
+2. A PO row carries the package icon; the primary line shows the PO number + vendor, and the row shows a status badge (Ordered / Received) with the total and created date.
+3. PO results are gated by Vendor &amp; Order Management: View.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 / 6.1 (Purchase Orders row), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>section 5.3 / 6.1 (Purchase Orders row)</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Vendor Invoices searchable; tri-state payment badge; no quick action</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Vendor Invoices Entity (v2)</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Vendor &amp; Order Management access.
 2. Vendor invoices exist in unpaid, partially paid and paid states.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Open global search and search for a vendor invoice.
 2. Look at the Vendor Invoices group, the row and its payment badge.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Vendor Invoices appear as their own searchable entity, grouped under a "Vendor Invoices" heading with a true count and a scope tab (subject to permission).
-2. A vendor-invoice row carries the file-text icon and shows a payment badge that is TRI-STATE: Unpaid, Partially paid, or Paid (not a binary paid/unpaid).
-3. A vendor-invoice row offers no hover quick action.
-4. Vendor Invoice results are gated by Vendor &amp; Order Management: View, and the invoice total is masked for a user without See Financial Data.
----
-This is the expected behaviour as per epic SV-9160 and story SV-9162 (BE search endpoint) / SV-9170 (result rows) and the Global Search PRD (Confluence page 576978945, version 1.1) and the Global Search v2 Technical Implementation Plan (FR-002, FR-014, NFR-005), read on 21 August 2026. The tech plan is Product-backed (Branko's PRD v1.1 + new 9-entity design, 2026-08-17/19) and, where it departs from stale PRD body text, wins by latest-authoritative-source (Rules 32/57).
-AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
-</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>requirements.md (Global Search PRD 576978945 v1.1 / tech plan v2)</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1. Vendor Invoices appear as their own searchable entity, grouped under a 'Vendor Invoices' heading with a true count and a scope tab (subject to permission).
+2. A vendor-invoice row carries the file-text icon; the primary line shows the invoice number + vendor, with a status badge (Paid / Unpaid), the total, the invoice date, and the type (Invoice / Sublet).
+3. Vendor Invoice results are gated by Vendor &amp; Order Management: View, and the invoice total is masked for a user without See Financial Data.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 / 6.1 (Vendor Invoices row), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>section 5.3 / 6.1 (Vendor Invoices row)</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/global-search-v2-testrail-import.xlsx
+++ b/testrail-import/global-search-v2-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4002,7 +4002,7 @@
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The Work Orders list filters to only rows matching 'Fib'.
-2. A blue banner reads 'Showing 12 work orders matching \'Fib\'' (the count reflects the number of matches).
+2. A blue banner reads 'Showing 12 work orders matching "Fib"' (the count reflects the number of matches).
 3. A 'Clear search' link appears on the right of the banner.
 4. The list columns remain: On Site, Status, Number, Customer, Asset, Unit, VIN/Serial #, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total Price.
 ---
@@ -5964,53 +5964,106 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>Search impressions and clicks are recorded (search-event telemetry)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Search Telemetry</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>The global search palette is available and returns results.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Run a query so results are shown (impressions).
+Click a result.
+Have engineering/QA confirm the search-event log.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1. Each result impression is logged with the query, result entity type, result id and position.
+2. A click on a result is logged as was_clicked for that result.
+3. This is mechanism/schema only - no ML ranking model is expected in v1.
+4. SCOPE NOTE (PO-GS-5): the owning story SV-9167 is currently in the backlog. If event logging is not present on the build, record it as a deviation to raise with Product - do not silently pass or ignore it.
+---
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (functional requirements) / 6.4 (telemetry schema), read on 25 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>section 8 / 6.4 (telemetry)</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>Vendor Invoices searchable; tri-state payment badge; no quick action</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Vendor Invoices Entity (v2)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in with Vendor &amp; Order Management access.
 2. Vendor invoices exist in unpaid, partially paid and paid states.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Open global search and search for a vendor invoice.
 2. Look at the Vendor Invoices group, the row and its payment badge.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. Vendor Invoices appear as their own searchable entity, grouped under a 'Vendor Invoices' heading with a true count and a scope tab (subject to permission).
-2. A vendor-invoice row carries the file-text icon; the primary line shows the invoice number + vendor, with a status badge (Paid / Unpaid), the total, the invoice date, and the type (Invoice / Sublet).
-3. Vendor Invoice results are gated by Vendor &amp; Order Management: View, and the invoice total is masked for a user without See Financial Data.
+2. A vendor-invoice row carries the file-text icon; the primary line shows the invoice number + vendor, with the total, the invoice date, and the type (Invoice / Sublet).
+3. The payment status badge per the spec (section 5.3) is Paid or Unpaid. KNOWN VARIANCE (PO-GS-6): if the build shows a third 'Partially paid' state, treat it as an expected variance to confirm with Product - do NOT fail the case on it.
+4. Vendor Invoice results are gated by Vendor &amp; Order Management: View, and the invoice total is masked for a user without See Financial Data.
 ---
 This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 / 6.1 (Vendor Invoices row), read on 25 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>section 5.3 / 6.1 (Vendor Invoices row)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/global-search-v2-testrail-import.xlsx
+++ b/testrail-import/global-search-v2-testrail-import.xlsx
@@ -529,7 +529,7 @@
 4. The placeholder reads a plain search placeholder (no 'ask a question' / AI wording in v1 - exact copy per the v2 design).
 5. The footer keyboard legend is visible: 'Navigate' with up/down arrows, 'Select' with the enter symbol, and 'Close esc'.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 Trigger and Surface; 8 Functional Requirements, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.1 Trigger and Surface; 8 Functional Requirements, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -581,7 +581,7 @@
 3. The input is focused and shows the placeholder a plain search placeholder (no 'ask a question' / AI wording in v1 - exact copy per the v2 design).
 4. The footer keyboard legend is visible.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 Trigger and Surface, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.1 Trigger and Surface, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -631,7 +631,7 @@
 2. The dimming is removed and you are back on the page you were on.
 3. Keyboard focus returns to the page (or the header search field).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1; 5.5 Keyboard Navigation, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.1; 5.5 Keyboard Navigation, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -680,7 +680,7 @@
           <t>1. The search box closes.
 2. The dimming is removed and you are back on the page.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 (Esc, clicking underlay, or Cmd+K again closes it), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.1 (Esc, clicking underlay, or Cmd+K again closes it), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -730,7 +730,7 @@
           <t>1. The search box closes.
 2. The dimming is removed and you are back on the page.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 (clicking the page underlay closes it), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.1 (clicking the page underlay closes it), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -783,7 +783,7 @@
 3. The highlight moves only across result rows - the group heading lines (for example 'Work orders (12)') are skipped and never get the highlight.
 4. When moving down past the last row of one group, the highlight continues into the first row of the next group.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.5 (Up/Down moves focus through visible rows, skipping group headers), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.5 (Up/Down moves focus through visible rows, skipping group headers), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -833,7 +833,7 @@
           <t>1. The palette closes and the highlighted record opens in the same browser tab.
 2. You land on that record's page (for example the Work Order detail page).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.5 (Enter opens the focused row in the same tab), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.5 (Enter opens the focused row in the same tab), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -883,7 +883,7 @@
           <t>1. The highlighted record opens in a NEW browser tab.
 2. The page you were on (and, per build behavior, the palette) remains in the original tab.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.5 (Cmd+Enter or Ctrl+Enter opens in a new browser tab), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.5 (Cmd+Enter or Ctrl+Enter opens in a new browser tab), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -937,7 +937,7 @@
 3. Selecting a tab scopes the results to that entity type.
 4. Focus does not leave the palette (focus stays trapped inside the modal).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.5 (Tab moves focus to the scope tab strip; Left/Right cycles tabs when focus is on the tab strip), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.5 (Tab moves focus to the scope tab strip; Left/Right cycles tabs when focus is on the tab strip), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -987,7 +987,7 @@
           <t>1. The footer keyboard legend is visible in every state: 'Navigate' with up/down arrows, 'Select' with the enter symbol, and 'Close esc'.
 2. The legend does not disappear when results are showing or when the input is empty.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 (footer always shows the keyboard legend), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.1 (footer always shows the keyboard legend), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1038,7 +1038,7 @@
 4. The strip scrolls horizontally since ten tabs do not fit the 640px modal width.
 5. A tab is shown only for an entity type the user has permission to see.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 (tab strip), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 (tab strip), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1089,7 +1089,7 @@
           <t>1. Results from every matching entity type appear, each under its own group heading with a true count (for example 'Work Orders (12)', 'Customers (2)').
 2. Groups appear in the v2 nine-entity order: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3; 6.2 group order, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 3; 6.2 group order, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1138,7 +1138,7 @@
           <t>1. Only Work Order results are shown; other entity groups (Customers, Assets, Parts, Vendors, Part Sales) are hidden.
 2. The 'Work Orders' tab appears selected/active.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3 (selecting a tab scopes the query to that entity type), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 3 (selecting a tab scopes the query to that entity type), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1187,7 +1187,7 @@
           <t>1. Only Customer results are shown; other entity groups are hidden.
 2. The 'Customers' tab appears selected/active.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 3, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1236,7 +1236,7 @@
           <t>1. Only Asset results are shown; other entity groups are hidden.
 2. The 'Assets' tab appears selected/active.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 3, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1285,7 +1285,7 @@
           <t>1. Only Part results are shown; other entity groups are hidden.
 2. The 'Parts' tab appears selected/active.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 3, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1334,7 +1334,7 @@
           <t>1. Only Vendor results are shown; other entity groups are hidden.
 2. The 'Vendors' tab appears selected/active.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 3, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1384,7 +1384,7 @@
           <t>1. Only Part Sales results are shown; other entity groups are hidden.
 2. The 'Part Sales' tab appears selected/active.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 (Part Sales is a NEW searchable entity); 5.2 State 3, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 4 (Part Sales is a NEW searchable entity); 5.2 State 3, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1437,7 +1437,7 @@
 2. Within the scoped tab the results carry that entity's true total count in the heading.
 3. When the scoped entity has more than five matches the same 'Show all N' link is available (full-page handoff per the Show-all case).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 (scope tab scoping), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 (scope tab scoping), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1485,7 +1485,7 @@
           <t>1. Selecting the 'Contacts' tab scopes the query to contacts only.
 2. The tab carries the true contact count; results show contact rows only.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.2 (Contacts scope tab), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.2 (Contacts scope tab), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1533,7 +1533,7 @@
           <t>1. Selecting the 'Purchase Orders' tab scopes the query to purchase orders only.
 2. The tab carries the true PO count; results show PO rows only (subject to permission).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.2 (Purchase Orders scope tab), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.2 (Purchase Orders scope tab), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1581,7 +1581,7 @@
           <t>1. Selecting the 'Vendor Invoices' tab scopes the query to vendor invoices only.
 2. The tab carries the true count; results show vendor-invoice rows only (subject to permission).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.2 (Vendor Invoices scope tab), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.2 (Vendor Invoices scope tab), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1631,7 +1631,7 @@
           <t>1. Each group heading shows the entity name and the total count in parentheses, for example 'Work orders (12)' and 'Customers (2)'.
 2. The count reflects the total number of matches for that entity type, even when only the first few rows are shown.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 3 (results grouped by entity type with a count), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 3 (results grouped by entity type with a count), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1681,7 +1681,7 @@
           <t>1. The group shows at most five result rows.
 2. It does not show six or more rows inline (the old behavior was three - it is now five).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 1 (old = 3 per category); 5.2 State 3 (up to 5 results), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 1 (old = 3 per category); 5.2 State 3 (up to 5 results), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1732,7 +1732,7 @@
 2. A group with five or fewer matches shows no 'Show all' link.
 3. The number N reflects the true total for that entity in the current query, not the capped five.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 (Show all N link), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 (Show all N link), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1784,7 +1784,7 @@
 4. While the handoff filter is active, the list page's own inline search field stays empty so the two filters are not confused.
 5. This is implemented for Work Orders in the prototype; each remaining entity list is expected to get the same treatment.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 (Show all - full-page handoff and results banner), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 (Show all - full-page handoff and results banner), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1834,7 +1834,7 @@
           <t>1. The groups appear top to bottom in this v2 nine-entity order: Work Orders, Customers, Contacts, Assets, Parts, Vendors, Part Sales, Purchase Orders, Vendor Invoices (D16).
 2. The order does not change based on how many matches each group has.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.2 (group display order in 'All'), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 6.2 (group display order in 'All'), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1884,7 +1884,7 @@
           <t>1. The matched substring 'Fib' is visually highlighted (in the captures it is highlighted in yellow) inside the result's primary text.
 2. Only the matched portion is highlighted, not the whole row.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 (matched substring highlighted), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.3 (matched substring highlighted), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1934,7 +1934,7 @@
           <t>1. The screen reader announces the total results count when it changes, for example 'X results found across N categories'.
 2. Every interactive element (input, tabs, rows, links) has a visible focus ring when reached by keyboard.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 Non-Functional (screen-reader announcements when results count changes; focus rings), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 9 Non-Functional (screen-reader announcements when results count changes; focus rings), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -1985,7 +1985,7 @@
 2. Within each group rows are sorted by score descending; ties break by recency.
 3. When the top result across all groups scores &gt; 0.95 (an ID match) it is pinned as a single row above the groups, carrying its entity icon.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), the section/story named in this case's References, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2038,7 +2038,7 @@
 4. A date is shown (for example 'Apr 27, 2026').
 5. A briefcase / work-order icon is shown on the left of the row.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Work Orders (Displayed: WO number + customer, status badge, lead technician, asset/unit, date), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 4 Work Orders (Displayed: WO number + customer, status badge, lead technician, asset/unit, date), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2090,7 +2090,7 @@
 3. A count chip is shown (the open work-order / document count, for example '12').
 4. A person icon is shown on the left of the row.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Customers (Displayed: name, address line, open WO count badge, telephone on hover), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 4 Customers (Displayed: name, address line, open WO count badge, telephone on hover), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2141,7 +2141,7 @@
 2. The owning customer name is shown as smaller secondary text (for example 'Bryan Smith').
 3. A vehicle icon is shown on the left of the row.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Assets (Displayed: year + make + model primary, customer name secondary), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 4 Assets (Displayed: year + make + model primary, customer name secondary), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2194,7 +2194,7 @@
 4. The quantity chip is colored by stock status: green when in stock, orange when low, red when out of stock.
 5. A tag / part icon is shown on the left of the row.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Parts (Displayed: description, part number, total quantity with stock-status color), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 4 Parts (Displayed: description, part number, total quantity with stock-status color), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2245,7 +2245,7 @@
 2. An address line is shown as the secondary line.
 3. A building icon is shown on the left of the row.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Vendors (Displayed: vendor name primary, address line secondary), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 4 Vendors (Displayed: vendor name primary, address line secondary), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2297,7 +2297,7 @@
 3. A total price and a created date are shown.
 4. A label icon is shown on the left of the row.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 Part Sales (Displayed: P-number + customer primary, status badge, total price + created date), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 4 Part Sales (Displayed: P-number + customer primary, status badge, total price + created date), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2348,7 +2348,7 @@
 2. Its secondary line shows 'Contact match' to indicate the match was on a contact field (phone or email) rather than the name.
 3. When the query reaches both a contact and its parent company, two rows are returned - the contact in the Contacts group and the company in its own group carrying the 'Contact match' label; neither row suppresses the other.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 4 (contact-field match), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 4 (contact-field match), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2398,7 +2398,7 @@
           <t>1. Status badge colors match the Work Order list tokens: Approved green, Estimate blue, Review yellow, In Progress blue, Completed gray, Declined red, Invoiced purple.
 2. Part stock badges use green (available), orange (low), red (out).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 (status badge colors, same tokens as the WO list), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.3 (status badge colors, same tokens as the WO list), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2448,7 +2448,7 @@
           <t>1. The 'Peterson' record is found and shown, despite the typo.
 2. The matched part of the text is highlighted.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (token n-gram / trigram matching catches Petersn -&gt; Peterson), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (token n-gram / trigram matching catches Petersn -&gt; Peterson), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2497,7 +2497,7 @@
         <is>
           <t>1. The 'Aabridge' record is found and shown, despite the typo.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 1 + 10 Phase 5 (fuzzy query 'Abrige'), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 1 + 10 Phase 5 (fuzzy query 'Abrige'), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2546,7 +2546,7 @@
         <is>
           <t>1. The 'Freightliner' record is found and shown, despite the transposed letters.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (Damerau-Levenshtein; freihgtliner -&gt; freightliner), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (Damerau-Levenshtein; freihgtliner -&gt; freightliner), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2595,7 +2595,7 @@
         <is>
           <t>1. The 'Fibridge' record is found and shown (matched by sound, as a last-resort phonetic match), likely lower in the ranking than an exact/near-exact match.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (phonetic fallback catches Filbridge -&gt; Fibridge), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (phonetic fallback catches Filbridge -&gt; Fibridge), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2647,7 +2647,7 @@
 2. The Work Order number is treated as an identifier: it is normalized by stripping the dash/space, so 'S2-15276' equals 's215276'.
 3. The match is exact (identifier), not fuzzy.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (S2-15276 = s215276); identifier fields are exact-only, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (S2-15276 = s215276); identifier fields are exact-only, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2697,7 +2697,7 @@
           <t>1. The exact VIN (case and spacing normalized) finds the matching asset / work order.
 2. A VIN with a wrong character does NOT return a fuzzy match - VINs are exact-only identifiers, no typo tolerance.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2748,7 +2748,7 @@
 2. The phone is normalized to digits only, so '(264) 328-6723' equals '2643286723'.
 3. The matched customer's secondary line shows 'Contact/info match' (matched on a contact field, not the name).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (phone normalization); 4 (Contact/info match affordance), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (phone normalization); 4 (Contact/info match affordance), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2798,7 +2798,7 @@
           <t>1. The exact part number finds the matching part.
 2. A part number with a wrong digit does NOT return a fuzzy match - part numbers are exact-only identifiers.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (What is NOT fuzzy: part number), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (What is NOT fuzzy: part number), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2848,7 +2848,7 @@
           <t>1. The real Work Order 'S2-15276' is NOT returned as a fuzzy match.
 2. Because identifier fields are exact-only, a one-digit-off WO number returns no fuzzy identifier match (it may show 'No results' if nothing else matches).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (exact identifier fields bypass fuzzy logic), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (exact identifier fields bypass fuzzy logic), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2898,7 +2898,7 @@
           <t>1. The matched token is highlighted.
 2. A subtle soft-match indicator is shown for fuzzy matches (spec mentions a '≈' symbol or italic treatment).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (fuzzy soft-match highlight treatment - design polish, confirm with design), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (fuzzy soft-match highlight treatment - design polish, confirm with design), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2948,7 +2948,7 @@
           <t>1. The exact P-number 'P2-58' finds the matching Part Sale.
 2. A one-digit-off P-number does NOT return the real Part Sale as a fuzzy match - P-numbers are exact-only identifiers, no typo tolerance (it may show 'No results' if nothing else matches).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (What is NOT fuzzy: VIN, WO number, P-number, part number - exact match after normalization), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -2998,7 +2998,7 @@
           <t>1. The exactly-matched Work Order is pinned as a single row at the very top, above the grouped results, labeled with its entity icon.
 2. This gives the 'type the number, jump straight to it' experience.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.2 (ID match &gt; 0.95 pinned at top), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 6.2 (ID match &gt; 0.95 pinned at top), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3048,7 +3048,7 @@
           <t>1. Open/active and recently-updated Work Orders rank above old, closed ones.
 2. Work Orders assigned to or recently viewed by the signed-in user are boosted; closed/Invoiced Work Orders older than 90 days are pushed down.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.1 Work Orders signals (open status +0.30, recency, assigned/viewed, old-closed demoted), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 6.1 Work Orders signals (open status +0.30, recency, assigned/viewed, old-closed demoted), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3098,7 +3098,7 @@
           <t>1. The in-stock part ranks above the out-of-stock part.
 2. The out-of-stock part is still shown (out-of-stock parts are not demoted below relevance and are not hidden).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.1 Parts signals, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 6.1 Parts signals, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3148,7 +3148,7 @@
           <t>1. Assets and Work Orders owned by the customer whose page you are on are boosted (appear higher) compared to the same search run from an unrelated page.
 2. This is a lightweight, single contextual-bias signal.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.3 Contextual bias, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 6.3 Contextual bias, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3198,7 +3198,7 @@
           <t>1. Parts already on that work order are pushed down (demoted) relative to other matching parts.
 2. Other parts in the same category as the work order's existing parts get a small boost.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.3 Contextual bias, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 6.3 Contextual bias, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3247,7 +3247,7 @@
 2. More recently created POs rank above older ones (recency decays over about two weeks).
 3. A PO created by the signed-in user gets a small additional boost.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 6.1 (Purchase Order signals), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 6.1 (Purchase Order signals), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3295,7 +3295,7 @@
           <t>1. An Unpaid vendor invoice ranks above paid ones.
 2. More recent invoice dates rank higher (recency decays over about a month).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 6.1 (Vendor Invoice signals), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 6.1 (Vendor Invoice signals), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3344,7 +3344,7 @@
 2. A contact called or viewed by the signed-in user in the last 7 days gets a boost.
 3. A company's primary contact gets a small additional boost.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 6.1 (Contact signals), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 6.1 (Contact signals), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3396,7 +3396,7 @@
 3. Three quick-create buttons are shown: 'New work order', 'New customer', 'New inventory part'.
 4. The footer keyboard legend is visible: down/up Navigate, Enter Select, Esc Close.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.1 / 5.2 (first-time state and placeholder copy), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.1 / 5.2 (first-time state and placeholder copy), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3448,7 +3448,7 @@
 3. 'New inventory part' starts the create-inventory-part flow.
 4. None of the buttons perform a destructive action.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 1 (quick-create chips), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 1 (quick-create chips), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3499,7 +3499,7 @@
 2. Rows are grouped under time headings: 'Today', 'Yesterday', 'Past week', 'Past 30 days'.
 3. Each row is a previously opened record (not just a previous search word).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 2 (Recent searches grouped by interval); 8 (persist recent-entity-views 30 days), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 2 (Recent searches grouped by interval); 8 (persist recent-entity-views 30 days), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3550,7 +3550,7 @@
 2. Each recent row uses the same row template as a normal result row (icon, primary line, secondary line, status/quantity cluster).
 3. Example rows: WO 'S1-644 Fisquare Farms' [Approved], Asset '2025 Freightliner M2 - Bryan Smith', Customer 'Adale Transport' with a doc chip, Part 'Rear Shock 65547' [72], Vendor 'Report Beverages'.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 2 (same row template as a result row), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 2 (same row template as a result row), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3599,7 +3599,7 @@
           <t>1. The palette closes and the clicked record opens.
 2. Opening the record refreshes its position in recent activity (it is 'touched').
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 4 (records a touch on every result click / entity-page visit), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 10 Phase 4 (records a touch on every result click / entity-page visit), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3649,7 +3649,7 @@
 3. After clearing, the panel falls back to the first-time state - helper text plus the three quick-create buttons - with no separate empty-history message.
 4. 'Clear all' is present on both web and mobile.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.2 / 5.6 / 8 (Clear all), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.2 / 5.6 / 8 (Clear all), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3702,7 +3702,7 @@
 3. The list is deduplicated: re-viewing an entity moves it to the top rather than adding a duplicate.
 4. A deleted entity is excluded from the recents list.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), the section/story named in this case's References, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3753,7 +3753,7 @@
           <t>1. After closing, the header search field still shows the last query 'Fibridge' as plain text.
 2. A small count badge (for example '1') is shown beside the persisted query.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 5 (Persisting search); 8 (persist last query, rehydrate on reopen), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 5 (Persisting search); 8 (persist last query, rehydrate on reopen), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3804,7 +3804,7 @@
 3. The result list for that query is shown again.
 4. The query text may appear selected/highlighted in the input so it can be replaced by typing.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 5 (Reopening restores the query, the scope tab, and the result list), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 5 (Reopening restores the query, the scope tab, and the result list), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3854,7 +3854,7 @@
 2. The results clear and the palette returns to the empty / recent-activity state (placeholder a plain search placeholder (no 'ask a question' / AI wording in v1 - exact copy per the v2 design)).
 3. The persisted query is removed from the header field.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 5; design-notes screenshot 9 (clearable via the x button), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 5; design-notes screenshot 9 (clearable via the x button), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3905,7 +3905,7 @@
 2. The three quick-create buttons are shown: 'New work order', 'New customer', 'New inventory part'.
 3. The footer keyboard legend is still visible.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 4 (No results for [query] + quick-create chips), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 4 (No results for [query] + quick-create chips), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -3954,7 +3954,7 @@
           <t>1. The matching create flow starts (create work order / customer / inventory part).
 2. No destructive action occurs.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.2 State 4, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.2 State 4, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4006,7 +4006,7 @@
 3. A 'Clear search' link appears on the right of the banner.
 4. The list columns remain: On Site, Status, Number, Customer, Asset, Unit, VIN/Serial #, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total Price.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), design-notes screenshot 1 (in-page Work Orders list search banner), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), design-notes screenshot 1 (in-page Work Orders list search banner), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4055,7 +4055,7 @@
           <t>1. The filter is removed and the full Work Orders list is shown again.
 2. The 'Showing N work orders matching [q]' banner is removed.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), design-notes screenshot 1, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), design-notes screenshot 1, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4107,7 +4107,7 @@
 2. The palette degrades gracefully - it does not crash or show a blank screen.
 3. Retrying after connectivity is restored re-runs the search and shows results.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (tolerate offline/network failures with an inline 'Search unavailable, retry' banner), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 8 (tolerate offline/network failures with an inline 'Search unavailable, retry' banner), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4157,7 +4157,7 @@
           <t>1. A 'Parts' group appears with matching part rows.
 2. The 'Parts' scope tab shows the part results.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (all result fields respect role-based-access checks), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 9 (all result fields respect role-based-access checks), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4208,7 +4208,7 @@
 2. The user cannot see part results they are not permitted to access, even though those parts exist.
 3. Results for entity types the user CAN access still appear normally.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (a technician without Parts access does not see Parts results), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 9 (a technician without Parts access does not see Parts results), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4258,7 +4258,7 @@
           <t>1. No 'Work orders' group appears and no Work Order rows are shown.
 2. Results for entity types the user CAN access still appear normally.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (all result fields respect role-based-access checks), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 9 (all result fields respect role-based-access checks), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4308,7 +4308,7 @@
           <t>1. Only records belonging to your own tenant/organization are returned.
 2. No records from any other tenant are shown (tenant isolation is respected).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (all result fields respect existing tenant-isolation checks), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 9 (all result fields respect existing tenant-isolation checks), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4360,7 +4360,7 @@
 2. Groups for the entity types that do have matches still appear normally.
 3. The empty entity type's scope tab shows its empty / no-results treatment rather than an error.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (must work for a single-tenant dataset where any entity type is empty, e.g. no part sales yet), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 9 (must work for a single-tenant dataset where any entity type is empty, e.g. no part sales yet), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4413,7 +4413,7 @@
 3. Without See Financial Data every price field is masked in results (part purchase/sell price, part-sale total, WO total, PO total, vendor-invoice total); masked values are never sent in the response.
 4. The TimeClock role gets an empty result set.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), the section/story named in this case's References, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4464,7 +4464,7 @@
 2. The body is a grouped, ranked, scored payload containing groups for the matching entity types.
 3. Each group includes the per-item metadata needed to render rows without extra fetches.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 1 (GET /api/search; scope=all), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 10 Phase 1 (GET /api/search; scope=all), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4516,7 +4516,7 @@
 2. Each response contains results only for the requested scope's entity type.
 3. The accepted scope values are all, work_orders, customers, assets, parts, vendors, part_sales.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 1 (scope parameter), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 10 Phase 1 (scope parameter), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4568,7 +4568,7 @@
 2. Each group reports its full total count (for example total 12) even though only 5 rows are returned.
 3. Setting limit changes the per-group cap accordingly.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 1 (limit default 5; response includes per-group totals), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 10 Phase 1 (limit default 5; response includes per-group totals), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4621,7 +4621,7 @@
 2. The identifier is normalized (case, diacritics, non-alphanumerics stripped) before matching.
 3. The exact-match result scores high enough to be flagged as the pinned top match (score above 0.95).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (identifier normalization); 6.2 (ID match pinned), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (identifier normalization); 6.2 (ID match pinned), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4671,7 +4671,7 @@
           <t>1. The real Work Order 'S2-15276' is NOT returned as a fuzzy identifier match.
 2. Identifier fields (VIN, WO number, P-number, part number) require exact match after normalization; fuzzy logic is bypassed for them.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 7 (What is NOT fuzzy), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 7 (What is NOT fuzzy), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4723,7 +4723,7 @@
 2. Scoping directly to 'parts' still returns no forbidden parts (empty or a permission-appropriate response).
 3. Entity types the user is allowed to access are still returned.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 9 (results respect role-based-access checks - enforced server-side), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 9 (results respect role-based-access checks - enforced server-side), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4775,7 +4775,7 @@
 2. A backend failure returns a 5xx or error payload that the frontend maps to the inline 'Search unavailable, retry' banner.
 3. The endpoint fails gracefully rather than returning malformed data.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (offline/network failure handling), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 8 (offline/network failure handling), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4826,7 +4826,7 @@
 2. Within each group items are ordered by score descending; ties break by recency.
 3. Each item carries the metadata needed to render its row (entity type, primary/secondary fields, badges/quantity, score) without extra fetches, and true per-group totals.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.2 (group order); 10 Phase 1 (per-item metadata), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 6.2 (group order); 10 Phase 1 (per-item metadata), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4878,7 +4878,7 @@
 2. Passing the cursor returns the next page of scoped results (no duplicates, no gaps).
 3. Pagination applies to the scoped-tab view.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 10 Phase 1 (cursor parameter), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 10 Phase 1 (cursor parameter), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4929,7 +4929,7 @@
           <t>1. With the customer context, assets and work orders owned by that customer are boosted in the ranking versus the no-context call.
 2. The context parameter takes an optional {type, id} for page-context bias.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 6.3 (contextual bias); 10 Phase 1 (context parameter), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 6.3 (contextual bias); 10 Phase 1 (context parameter), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -4980,7 +4980,7 @@
 2. GET /user/recent-entities returns the recently touched records, retained for 30 days.
 3. The results support bucketing into Today / Yesterday / Past week / Past 30 days at render time.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (persist recent-entity-views 30 days); 10 Phase 4, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 8 (persist recent-entity-views 30 days); 10 Phase 4, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5031,7 +5031,7 @@
           <t>1. The backend is not queried on every keystroke; input is debounced (about 150ms) so a request fires after a short pause.
 2. Grouped results render quickly once the response arrives (target within about 200ms at p95).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (debounce input at 150ms; render within 200ms p95), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 8 (debounce input at 150ms; render within 200ms p95), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5083,7 +5083,7 @@
 3. A contact row carries the contact (user-round) icon, the contact name (primary), and its company/context (secondary); a match on phone/email carries the "Contact/info match" flag.
 4. Company-less contacts (no company_id) are not indexed and do not appear.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), the section/story named in this case's References, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5135,7 +5135,7 @@
 3. Adding a new searchable entity is a single provider class plus mapping (framework extensibility), so page and global search stay in lockstep.
 4. Exports keep their current data path in v1 (not cut over).
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), the section/story named in this case's References, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5186,7 +5186,7 @@
 2. The old GET /api/global-search/fetch endpoint, its handler and the client-side filtering are removed after stabilisation.
 3. The 3-result-per-category dropdown behaviour is replaced entirely by the modal.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), the section/story named in this case's References, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5237,7 +5237,7 @@
 2. The action is non-destructive.
 ---
 EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Work Order -&gt; 'Add new line', only when currently editing a WO elsewhere), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.4 (Work Order -&gt; 'Add new line', only when currently editing a WO elsewhere), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5289,7 +5289,7 @@
 3. The actions are non-destructive.
 ---
 EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Asset -&gt; 'New work order' + clock (history) and Invoice icons), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.4 (Asset -&gt; 'New work order' + clock (history) and Invoice icons), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5341,7 +5341,7 @@
 3. The actions are non-destructive.
 ---
 EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Customer -&gt; 'New work order', 'New contact'), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.4 (Customer -&gt; 'New work order', 'New contact'), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5394,7 +5394,7 @@
 3. The action is non-destructive.
 ---
 EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Part -&gt; 'Add part' when not currently editing a WO), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.4 (Part -&gt; 'Add part' when not currently editing a WO), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5445,7 +5445,7 @@
 2. The action is non-destructive.
 ---
 EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Vendor -&gt; 'Add contact'), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.4 (Vendor -&gt; 'Add contact'), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5497,7 +5497,7 @@
 2. Using it adds the part to the work order you are editing (an inline add, non-destructive).
 ---
 EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Part -&gt; 'Add to work order' only when currently editing a WO), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.4 (Part -&gt; 'Add to work order' only when currently editing a WO), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5547,7 +5547,7 @@
 2. Every action offered by a quick action is also reachable from the entity's full record (hover is non-essential).
 ---
 EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.4 (Quick actions never trigger destructive operations; hover state non-essential), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.4 (Quick actions never trigger destructive operations; hover state non-essential), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5599,7 +5599,7 @@
 3. The "currently editing a WO" state comes from the shared page-context source.
 ---
 EXCLUDED FROM V1 - not tested in this release. Contextual quick actions on result rows are a v1 non-goal: the Global Search PRD v1.2 documents the intended behaviour in section 5.4 but states it “is not part of the v1 build and carries no v1 stories” (see also section 2, Non-Goals). Kept for the future release in which quick actions are built - do not execute against the v1 build.
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), the section/story named in this case's References, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5652,7 +5652,7 @@
 3. Quick actions remain reachable on touch (no hover) via the design's touch affordance.
 4. The tab strip remains usable with up to ten tabs on a narrow viewport.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), the section/story named in this case's References, read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), the section/story named in this case's References, read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5702,7 +5702,7 @@
 3. The placeholder copy is 'Search everything'.
 4. There is no keyboard-hints footer on mobile.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile surface), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.6 (mobile surface), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5751,7 +5751,7 @@
 2. The chip row appears only once there is a query.
 3. It lists only the entity types that actually matched, each with its count, so the row stays short.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile scope chips), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.6 (mobile scope chips), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5801,7 +5801,7 @@
 3. Group headers stick to the top of the list while scrolling.
 4. A tap on a row opens the record.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile results), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.6 (mobile results), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5850,7 +5850,7 @@
 2. The quick-create buttons are stacked full-width instead of inline.
 3. 'Clear all' behaves as on web: clearing the history returns the screen to the first-time state.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile states), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.6 (mobile states), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5898,7 +5898,7 @@
           <t>1. The full-page result handoff and its banner (the web 'Show all' behaviour) do not apply on mobile in v1 - the mobile lists have no query handoff.
 2. Keyboard navigation does not apply on mobile.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), 5.6 (mobile deferrals), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), 5.6 (mobile deferrals), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -5949,7 +5949,7 @@
 2. A PO row carries the package icon; the primary line shows the PO number + vendor, and the row shows a status badge (Ordered / Received) with the total and created date.
 3. PO results are gated by Vendor &amp; Order Management: View.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 / 6.1 (Purchase Orders row), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.3 / 6.1 (Purchase Orders row), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -6001,7 +6001,7 @@
 3. This is mechanism/schema only - no ML ranking model is expected in v1.
 4. SCOPE NOTE (PO-GS-5): the owning story SV-9167 is currently in the backlog. If event logging is not present on the build, record it as a deviation to raise with Product - do not silently pass or ignore it.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 8 (functional requirements) / 6.4 (telemetry schema), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 8 (functional requirements) / 6.4 (telemetry schema), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
@@ -6053,7 +6053,7 @@
 3. The payment status badge per the spec (section 5.3) is Paid or Unpaid. KNOWN VARIANCE (PO-GS-6): if the build shows a third 'Partially paid' state, treat it as an expected variance to confirm with Product - do NOT fail the case on it.
 4. Vendor Invoice results are gated by Vendor &amp; Order Management: View, and the invoice total is masked for a user without See Financial Data.
 ---
-This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 11), section 5.3 / 6.1 (Vendor Invoices row), read on 25 August 2026.
+This is the expected behaviour as per epic SV-9160 and the Global Search - Product Requirements specification version 1.2 (Confluence page 576978945, Confluence version 12), section 5.3 / 6.1 (Vendor Invoices row), read on 26 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
         </is>
       </c>
